--- a/scripts/generate_report_from_webgains/enriched_webgains_reports/Transacciones_newcop_2509_enriched.xlsx
+++ b/scripts/generate_report_from_webgains/enriched_webgains_reports/Transacciones_newcop_2509_enriched.xlsx
@@ -860,7 +860,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Essentials Hoodie (FW22) Light Oatmeal</t>
+          <t>Adidas Samba OG Maroon Off White Gum</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
@@ -875,7 +875,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Adidas Samba OG Maroon Off White Gum</t>
+          <t>Essentials Hoodie (FW22) Light Oatmeal</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
@@ -965,7 +965,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Adidas Adizero Evo SL White Pure Teal</t>
+          <t>Puma Arizona SD Flat Bronze-Alpine Snow</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
@@ -980,7 +980,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Puma Arizona SD Flat Bronze-Alpine Snow</t>
+          <t>Essentials Pullover Hoodie (FW22) Stretch Limo/Black</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
@@ -995,7 +995,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Essentials Pullover Hoodie (FW22) Stretch Limo/Black</t>
+          <t>Adidas Adizero Evo SL White Pure Teal</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
@@ -1085,7 +1085,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Air Force 1 Rope Laces Black</t>
+          <t>Air Jordan 4 Retro OG SP Undefeated</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
@@ -1100,7 +1100,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Retro OG SP Undefeated</t>
+          <t>Air Force 1 Rope Laces Black</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
@@ -1419,22 +1419,22 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>127.5</v>
+        <v>70</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>7.65</v>
+        <v>4.2</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09/30/25 16:25</t>
+          <t>09/30/25 12:49</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>79375</t>
+          <t>79361</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Adidas Adizero Evo SL White Pure Teal</t>
+          <t>Puma Arizona SD Flat Bronze-Alpine Snow</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>42 EU - 8.5 US</t>
+          <t>37 EU - 5 US</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>JS4487</t>
+          <t>402362-04</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1485,24 +1485,20 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>protomela@yahoo.es</t>
+          <t>sandra.isla.88@gmail.com</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Jose luis</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Sanchis mañanos</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>+34671639303</t>
-        </is>
-      </c>
+          <t>Isla</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>First Order</t>
@@ -1540,26 +1536,26 @@
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
+          <t>Mathias Kraft</t>
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="C3" s="16" t="n">
-        <v>4.2</v>
+        <v>10.8</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>1.26</v>
+        <v>3.24</v>
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>09/30/25 12:49</t>
+          <t>09/30/25 15:30</t>
         </is>
       </c>
       <c r="F3" s="15" t="inlineStr">
         <is>
-          <t>79361</t>
+          <t>79365</t>
         </is>
       </c>
       <c r="G3" s="15" t="inlineStr">
@@ -1579,17 +1575,17 @@
       </c>
       <c r="J3" s="15" t="inlineStr">
         <is>
-          <t>Puma Arizona SD Flat Bronze-Alpine Snow</t>
+          <t>Essentials Pullover Hoodie (FW22) Stretch Limo/Black</t>
         </is>
       </c>
       <c r="K3" s="15" t="inlineStr">
         <is>
-          <t>37 EU - 5 US</t>
+          <t>M</t>
         </is>
       </c>
       <c r="L3" s="15" t="inlineStr">
         <is>
-          <t>402362-04</t>
+          <t>192BT212110F</t>
         </is>
       </c>
       <c r="M3" s="15" t="inlineStr">
@@ -1610,28 +1606,32 @@
       <c r="P3" s="15" t="inlineStr"/>
       <c r="Q3" s="15" t="inlineStr">
         <is>
-          <t>sandra.isla.88@gmail.com</t>
+          <t>gaizkablanco7@gmail.com</t>
         </is>
       </c>
       <c r="R3" s="15" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>Gaizka</t>
         </is>
       </c>
       <c r="S3" s="15" t="inlineStr">
         <is>
-          <t>Isla</t>
-        </is>
-      </c>
-      <c r="T3" s="15" t="inlineStr"/>
+          <t>Blanco</t>
+        </is>
+      </c>
+      <c r="T3" s="15" t="inlineStr">
+        <is>
+          <t>+34664564676</t>
+        </is>
+      </c>
       <c r="U3" s="15" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #3)</t>
         </is>
       </c>
       <c r="V3" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W3" s="15" t="inlineStr">
@@ -1639,21 +1639,9 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="X3" s="15" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="Y3" s="15" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="Z3" s="15" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
+      <c r="X3" s="15" t="inlineStr"/>
+      <c r="Y3" s="15" t="inlineStr"/>
+      <c r="Z3" s="15" t="inlineStr"/>
       <c r="AA3" s="15" t="inlineStr"/>
       <c r="AB3" s="15" t="inlineStr"/>
       <c r="AC3" s="15" t="inlineStr"/>
@@ -1661,26 +1649,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mathias Kraft</t>
+          <t>Digital Expand</t>
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>180</v>
+        <v>127.5</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>10.8</v>
+        <v>7.65</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>3.24</v>
+        <v>2.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>09/30/25 15:30</t>
+          <t>09/30/25 16:25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>79365</t>
+          <t>79375</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1700,17 +1688,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Essentials Pullover Hoodie (FW22) Stretch Limo/Black</t>
+          <t>Adidas Adizero Evo SL White Pure Teal</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>42 EU - 8.5 US</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>192BT212110F</t>
+          <t>JS4487</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1731,32 +1719,32 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>gaizkablanco7@gmail.com</t>
+          <t>protomela@yahoo.es</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Gaizka</t>
+          <t>Jose luis</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>Sanchis mañanos</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>+34664564676</t>
+          <t>+34671639303</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #3)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1764,9 +1752,21 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -2117,31 +2117,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Webravo SRL</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>330</v>
+        <v>110</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>19.8</v>
+        <v>6.6</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>5.94</v>
+        <v>1.98</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>09/24/25 14:24</t>
+          <t>09/22/25 20:03</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>78891</t>
+          <t>78812</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2156,17 +2156,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Denim Tears The Cotton Wreath Sweatshirt Black</t>
+          <t>Adidas Samba OG Maroon Off White Gum</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>39.3 EU - 6.5 US</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>DENIMBW</t>
+          <t>JR8844</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -2187,17 +2187,17 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>sandionisio7@gmail.com</t>
+          <t>ccarbonell.torrees@gmail.com</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Carlota</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Neira Parra</t>
+          <t>Carbonell Torres</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -2216,9 +2216,21 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -2472,31 +2484,31 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Webravo SRL</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>110</v>
+        <v>330</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>6.6</v>
+        <v>19.8</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>1.98</v>
+        <v>5.94</v>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>09/22/25 20:03</t>
+          <t>09/24/25 14:24</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>78812</t>
+          <t>78891</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
@@ -2511,17 +2523,17 @@
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
-          <t>Adidas Samba OG Maroon Off White Gum</t>
+          <t>Denim Tears The Cotton Wreath Sweatshirt Black</t>
         </is>
       </c>
       <c r="K11" s="15" t="inlineStr">
         <is>
-          <t>39.3 EU - 6.5 US</t>
+          <t>M</t>
         </is>
       </c>
       <c r="L11" s="15" t="inlineStr">
         <is>
-          <t>JR8844</t>
+          <t>DENIMBW</t>
         </is>
       </c>
       <c r="M11" s="15" t="inlineStr">
@@ -2542,17 +2554,17 @@
       <c r="P11" s="15" t="inlineStr"/>
       <c r="Q11" s="15" t="inlineStr">
         <is>
-          <t>ccarbonell.torrees@gmail.com</t>
+          <t>sandionisio7@gmail.com</t>
         </is>
       </c>
       <c r="R11" s="15" t="inlineStr">
         <is>
-          <t>Carlota</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="S11" s="15" t="inlineStr">
         <is>
-          <t>Carbonell Torres</t>
+          <t>Neira Parra</t>
         </is>
       </c>
       <c r="T11" s="15" t="inlineStr"/>
@@ -2571,21 +2583,9 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="X11" s="15" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="Y11" s="15" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="Z11" s="15" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
+      <c r="X11" s="15" t="inlineStr"/>
+      <c r="Y11" s="15" t="inlineStr"/>
+      <c r="Z11" s="15" t="inlineStr"/>
       <c r="AA11" s="15" t="inlineStr"/>
       <c r="AB11" s="15" t="inlineStr"/>
       <c r="AC11" s="15" t="inlineStr"/>
@@ -2593,26 +2593,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
+          <t>Invoke AB</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>170</v>
+        <v>350</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>10.2</v>
+        <v>21</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>3.06</v>
+        <v>6.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>09/22/25 14:45</t>
+          <t>09/20/25 11:34</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6903116824917</t>
+          <t>6900010221909</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2632,17 +2632,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Air Force 1 Rope Laces Black</t>
+          <t>Air Jordan 4 Retro OG SP Undefeated</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>45 EU - 11 US</t>
+          <t>46 EU - 12 US</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CW2288-001-BLACK</t>
+          <t>IB1519-200</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2663,54 +2663,38 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>am.nieto.ro@gmail.com</t>
+          <t>blanco_negro1977@hotmail.com</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Ana María</t>
+          <t>Jorge</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Nieto Rodríguez</t>
+          <t>Lozano lozano</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>+34650261577</t>
+          <t>+34654624273</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #4)</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
@@ -2718,26 +2702,26 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
+          <t>Purplee Corp</t>
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>6</v>
+        <v>10.2</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>1.8</v>
+        <v>3.06</v>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>09/18/25 19:39</t>
+          <t>09/22/25 14:45</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>6897694179669</t>
+          <t>6903116824917</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -2747,27 +2731,27 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
-          <t>Puma Speedcat TTF Dark Chocolate Frosted Ivory</t>
+          <t>Air Force 1 Rope Laces Black</t>
         </is>
       </c>
       <c r="K13" s="15" t="inlineStr">
         <is>
-          <t>37 EU - 4.5 US</t>
+          <t>45 EU - 11 US</t>
         </is>
       </c>
       <c r="L13" s="15" t="inlineStr">
         <is>
-          <t>403903-01</t>
+          <t>CW2288-001-BLACK</t>
         </is>
       </c>
       <c r="M13" s="15" t="inlineStr">
@@ -2788,20 +2772,24 @@
       <c r="P13" s="15" t="inlineStr"/>
       <c r="Q13" s="15" t="inlineStr">
         <is>
-          <t>albertolagoalba@gmail.com</t>
+          <t>am.nieto.ro@gmail.com</t>
         </is>
       </c>
       <c r="R13" s="15" t="inlineStr">
         <is>
-          <t>Alberto</t>
+          <t>Ana María</t>
         </is>
       </c>
       <c r="S13" s="15" t="inlineStr">
         <is>
-          <t>Lago alba</t>
-        </is>
-      </c>
-      <c r="T13" s="15" t="inlineStr"/>
+          <t>Nieto Rodríguez</t>
+        </is>
+      </c>
+      <c r="T13" s="15" t="inlineStr">
+        <is>
+          <t>+34650261577</t>
+        </is>
+      </c>
       <c r="U13" s="15" t="inlineStr">
         <is>
           <t>First Order</t>
@@ -2817,9 +2805,21 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="X13" s="15" t="inlineStr"/>
-      <c r="Y13" s="15" t="inlineStr"/>
-      <c r="Z13" s="15" t="inlineStr"/>
+      <c r="X13" s="15" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="Y13" s="15" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="Z13" s="15" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
       <c r="AA13" s="15" t="inlineStr"/>
       <c r="AB13" s="15" t="inlineStr"/>
       <c r="AC13" s="15" t="inlineStr"/>
@@ -2827,26 +2827,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
+          <t>Digital Expand</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>6.3</v>
+        <v>1.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>09/20/25 11:34</t>
+          <t>09/18/25 19:39</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6900010221909</t>
+          <t>6897694179669</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2856,27 +2856,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Retro OG SP Undefeated</t>
+          <t>Puma Speedcat TTF Dark Chocolate Frosted Ivory</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>46 EU - 12 US</t>
+          <t>37 EU - 4.5 US</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>IB1519-200</t>
+          <t>403903-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2897,35 +2897,35 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>blanco_negro1977@hotmail.com</t>
+          <t>albertolagoalba@gmail.com</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Jorge</t>
+          <t>Alberto</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Lozano lozano</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>+34654624273</t>
-        </is>
-      </c>
+          <t>Lago alba</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #4)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
@@ -2936,26 +2936,26 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Pashion.dk ApS</t>
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>1.98</v>
+        <v>4.2</v>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>09/19/25 23:39</t>
+          <t>09/16/25 20:51</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>78602</t>
+          <t>6894848966997</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
@@ -2965,27 +2965,27 @@
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
-          <t>Adidas Samba OG Maroon Off White Gum</t>
+          <t>Air Jordan 3 Retro Black Cat</t>
         </is>
       </c>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>40.6 EU - 7.5 US</t>
+          <t>36.5 EU - 4.5 US</t>
         </is>
       </c>
       <c r="L15" s="15" t="inlineStr">
         <is>
-          <t>JR8844</t>
+          <t>CT8532-001</t>
         </is>
       </c>
       <c r="M15" s="15" t="inlineStr">
@@ -3006,28 +3006,32 @@
       <c r="P15" s="15" t="inlineStr"/>
       <c r="Q15" s="15" t="inlineStr">
         <is>
-          <t>anamariamenzr1@hotmail.com</t>
+          <t>restauracionespablogarcia@hotmail.com</t>
         </is>
       </c>
       <c r="R15" s="15" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="S15" s="15" t="inlineStr">
         <is>
-          <t>Menezo Rojas</t>
-        </is>
-      </c>
-      <c r="T15" s="15" t="inlineStr"/>
+          <t>Liaño cobo</t>
+        </is>
+      </c>
+      <c r="T15" s="15" t="inlineStr">
+        <is>
+          <t>+34699813897</t>
+        </is>
+      </c>
       <c r="U15" s="15" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #2)</t>
         </is>
       </c>
       <c r="V15" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W15" s="15" t="inlineStr">
@@ -3035,21 +3039,9 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="X15" s="15" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="Y15" s="15" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="Z15" s="15" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
+      <c r="X15" s="15" t="inlineStr"/>
+      <c r="Y15" s="15" t="inlineStr"/>
+      <c r="Z15" s="15" t="inlineStr"/>
       <c r="AA15" s="15" t="inlineStr"/>
       <c r="AB15" s="15" t="inlineStr"/>
       <c r="AC15" s="15" t="inlineStr"/>
@@ -3057,26 +3049,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Webravo SRL</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>09/20/25 11:53</t>
+          <t>09/19/25 23:39</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>78608</t>
+          <t>78602</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3096,17 +3088,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Adidas Samba Jane Cream Black Gum</t>
+          <t>Adidas Samba OG Maroon Off White Gum</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>38 EU - 5.5 US</t>
+          <t>40.6 EU - 7.5 US</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>JR7338</t>
+          <t>JR8844</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -3127,17 +3119,17 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>paulalopezpuyol12@gmail.com</t>
+          <t>anamariamenzr1@hotmail.com</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>López Puyol</t>
+          <t>Menezo Rojas</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -3178,26 +3170,26 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Pashion.dk ApS</t>
+          <t>Webravo SRL</t>
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>280</v>
+        <v>90</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>09/16/25 20:51</t>
+          <t>09/20/25 11:53</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>6894848966997</t>
+          <t>78608</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -3207,27 +3199,27 @@
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
-          <t>Air Jordan 3 Retro Black Cat</t>
+          <t>Adidas Samba Jane Cream Black Gum</t>
         </is>
       </c>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>36.5 EU - 4.5 US</t>
+          <t>38 EU - 5.5 US</t>
         </is>
       </c>
       <c r="L17" s="15" t="inlineStr">
         <is>
-          <t>CT8532-001</t>
+          <t>JR7338</t>
         </is>
       </c>
       <c r="M17" s="15" t="inlineStr">
@@ -3248,32 +3240,28 @@
       <c r="P17" s="15" t="inlineStr"/>
       <c r="Q17" s="15" t="inlineStr">
         <is>
-          <t>restauracionespablogarcia@hotmail.com</t>
+          <t>paulalopezpuyol12@gmail.com</t>
         </is>
       </c>
       <c r="R17" s="15" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="S17" s="15" t="inlineStr">
         <is>
-          <t>Liaño cobo</t>
-        </is>
-      </c>
-      <c r="T17" s="15" t="inlineStr">
-        <is>
-          <t>+34699813897</t>
-        </is>
-      </c>
+          <t>López Puyol</t>
+        </is>
+      </c>
+      <c r="T17" s="15" t="inlineStr"/>
       <c r="U17" s="15" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #2)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="V17" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" s="15" t="inlineStr">
@@ -3281,9 +3269,21 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="X17" s="15" t="inlineStr"/>
-      <c r="Y17" s="15" t="inlineStr"/>
-      <c r="Z17" s="15" t="inlineStr"/>
+      <c r="X17" s="15" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="Y17" s="15" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="Z17" s="15" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
       <c r="AA17" s="15" t="inlineStr"/>
       <c r="AB17" s="15" t="inlineStr"/>
       <c r="AC17" s="15" t="inlineStr"/>
@@ -3400,26 +3400,26 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Pashion.dk ApS</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>6</v>
+        <v>5.28</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>09/16/25 16:05</t>
+          <t>09/15/25 11:50</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>78437</t>
+          <t>78383</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
@@ -3429,27 +3429,27 @@
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
-          <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
+          <t>Puma Speedcat OG Haute Coffee Frosted Ivory</t>
         </is>
       </c>
       <c r="K19" s="15" t="inlineStr">
         <is>
-          <t>41 EU - 8.5 US</t>
+          <t>37 EU - 5 US</t>
         </is>
       </c>
       <c r="L19" s="15" t="inlineStr">
         <is>
-          <t>310864-01</t>
+          <t>398846-31</t>
         </is>
       </c>
       <c r="M19" s="15" t="inlineStr">
@@ -3470,32 +3470,28 @@
       <c r="P19" s="15" t="inlineStr"/>
       <c r="Q19" s="15" t="inlineStr">
         <is>
-          <t>alfredirriak24@gmail.com</t>
+          <t>ilargi-betea22@hotmail.com</t>
         </is>
       </c>
       <c r="R19" s="15" t="inlineStr">
         <is>
-          <t>Alfredo Dueñas</t>
+          <t>Elisabet</t>
         </is>
       </c>
       <c r="S19" s="15" t="inlineStr">
         <is>
-          <t>Fernández</t>
-        </is>
-      </c>
-      <c r="T19" s="15" t="inlineStr">
-        <is>
-          <t>+34613250693</t>
-        </is>
-      </c>
+          <t>Menen</t>
+        </is>
+      </c>
+      <c r="T19" s="15" t="inlineStr"/>
       <c r="U19" s="15" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #2)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="V19" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" s="15" t="inlineStr">
@@ -3503,21 +3499,9 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="X19" s="15" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="Y19" s="15" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="Z19" s="15" t="inlineStr">
-        <is>
-          <t>20498453736</t>
-        </is>
-      </c>
+      <c r="X19" s="15" t="inlineStr"/>
+      <c r="Y19" s="15" t="inlineStr"/>
+      <c r="Z19" s="15" t="inlineStr"/>
       <c r="AA19" s="15" t="inlineStr"/>
       <c r="AB19" s="15" t="inlineStr"/>
       <c r="AC19" s="15" t="inlineStr"/>
@@ -3634,26 +3618,26 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Pashion.dk ApS</t>
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>5.28</v>
+        <v>6</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>09/15/25 11:50</t>
+          <t>09/16/25 16:05</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>78383</t>
+          <t>78437</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -3663,27 +3647,27 @@
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
-          <t>Puma Speedcat OG Haute Coffee Frosted Ivory</t>
+          <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
         </is>
       </c>
       <c r="K21" s="15" t="inlineStr">
         <is>
-          <t>37 EU - 5 US</t>
+          <t>41 EU - 8.5 US</t>
         </is>
       </c>
       <c r="L21" s="15" t="inlineStr">
         <is>
-          <t>398846-31</t>
+          <t>310864-01</t>
         </is>
       </c>
       <c r="M21" s="15" t="inlineStr">
@@ -3704,28 +3688,32 @@
       <c r="P21" s="15" t="inlineStr"/>
       <c r="Q21" s="15" t="inlineStr">
         <is>
-          <t>ilargi-betea22@hotmail.com</t>
+          <t>alfredirriak24@gmail.com</t>
         </is>
       </c>
       <c r="R21" s="15" t="inlineStr">
         <is>
-          <t>Elisabet</t>
+          <t>Alfredo Dueñas</t>
         </is>
       </c>
       <c r="S21" s="15" t="inlineStr">
         <is>
-          <t>Menen</t>
-        </is>
-      </c>
-      <c r="T21" s="15" t="inlineStr"/>
+          <t>Fernández</t>
+        </is>
+      </c>
+      <c r="T21" s="15" t="inlineStr">
+        <is>
+          <t>+34613250693</t>
+        </is>
+      </c>
       <c r="U21" s="15" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #2)</t>
         </is>
       </c>
       <c r="V21" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W21" s="15" t="inlineStr">
@@ -3733,9 +3721,21 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="X21" s="15" t="inlineStr"/>
-      <c r="Y21" s="15" t="inlineStr"/>
-      <c r="Z21" s="15" t="inlineStr"/>
+      <c r="X21" s="15" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="Y21" s="15" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="Z21" s="15" t="inlineStr">
+        <is>
+          <t>20498453736</t>
+        </is>
+      </c>
       <c r="AA21" s="15" t="inlineStr"/>
       <c r="AB21" s="15" t="inlineStr"/>
       <c r="AC21" s="15" t="inlineStr"/>
@@ -3743,26 +3743,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pashion.dk ApS</t>
+          <t>Purplee Corp</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>120</v>
+        <v>82.5</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>6</v>
+        <v>4.95</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>09/15/25 11:46</t>
+          <t>09/14/25 12:50</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>78382</t>
+          <t>6891134681429</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3772,27 +3772,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Puma Speedcat TTF Dark Chocolate Frosted Ivory</t>
+          <t>Adidas Handball Spezial Core Black Pink</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>41 EU - 8 US</t>
+          <t>43.3 EU - 9.5 US</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>403903-01</t>
+          <t>IE5897</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3813,24 +3813,20 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>luiscompostizo@gmail.com</t>
+          <t>Slwoffi@hotmail.com</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Compostizo Garcia</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>+34722237884</t>
-        </is>
-      </c>
+          <t>Lwoff Ivanissevich</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
           <t>First Order</t>
@@ -3841,16 +3837,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>webgains</t>
-        </is>
-      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
@@ -3860,26 +3848,26 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Pashion.dk ApS</t>
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>5.76</v>
+        <v>6</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>09/14/25 22:07</t>
+          <t>09/15/25 11:46</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>78374</t>
+          <t>78382</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
@@ -3889,27 +3877,27 @@
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="J23" s="15" t="inlineStr">
         <is>
-          <t>Adidas Samba OG Core Black</t>
+          <t>Puma Speedcat TTF Dark Chocolate Frosted Ivory</t>
         </is>
       </c>
       <c r="K23" s="15" t="inlineStr">
         <is>
-          <t>42.6 EU - 9 US</t>
+          <t>41 EU - 8 US</t>
         </is>
       </c>
       <c r="L23" s="15" t="inlineStr">
         <is>
-          <t>B75807</t>
+          <t>403903-01</t>
         </is>
       </c>
       <c r="M23" s="15" t="inlineStr">
@@ -3930,20 +3918,24 @@
       <c r="P23" s="15" t="inlineStr"/>
       <c r="Q23" s="15" t="inlineStr">
         <is>
-          <t>ydorgambide@gmail.com</t>
+          <t>luiscompostizo@gmail.com</t>
         </is>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
-          <t>Yago</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="S23" s="15" t="inlineStr">
         <is>
-          <t>Dorgambide Dios</t>
-        </is>
-      </c>
-      <c r="T23" s="15" t="inlineStr"/>
+          <t>Compostizo Garcia</t>
+        </is>
+      </c>
+      <c r="T23" s="15" t="inlineStr">
+        <is>
+          <t>+34722237884</t>
+        </is>
+      </c>
       <c r="U23" s="15" t="inlineStr">
         <is>
           <t>First Order</t>
@@ -3959,7 +3951,11 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="X23" s="15" t="inlineStr"/>
+      <c r="X23" s="15" t="inlineStr">
+        <is>
+          <t>webgains</t>
+        </is>
+      </c>
       <c r="Y23" s="15" t="inlineStr"/>
       <c r="Z23" s="15" t="inlineStr"/>
       <c r="AA23" s="15" t="inlineStr"/>
@@ -3969,26 +3965,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>82.5</v>
+        <v>96</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>4.95</v>
+        <v>5.76</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>09/14/25 12:50</t>
+          <t>09/14/25 22:07</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6891134681429</t>
+          <t>78374</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4008,17 +4004,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Adidas Handball Spezial Core Black Pink</t>
+          <t>Adidas Samba OG Core Black</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>43.3 EU - 9.5 US</t>
+          <t>42.6 EU - 9 US</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>IE5897</t>
+          <t>B75807</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -4039,17 +4035,17 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Slwoffi@hotmail.com</t>
+          <t>ydorgambide@gmail.com</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Yago</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Lwoff Ivanissevich</t>
+          <t>Dorgambide Dios</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -4063,7 +4059,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
@@ -4074,26 +4074,26 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Digital Expand</t>
         </is>
       </c>
       <c r="B25" s="16" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>37.5</v>
+        <v>27.5</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>11.25</v>
+        <v>8.25</v>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>09/13/25 10:43</t>
+          <t>09/11/25 16:14</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>78157</t>
+          <t>6887025475925</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -4113,17 +4113,17 @@
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
-          <t>Dunk Low Off-White Lot 21</t>
+          <t>Air Jordan 1 Retro Low OG SP Travis Scott Velvet Brown</t>
         </is>
       </c>
       <c r="K25" s="15" t="inlineStr">
         <is>
-          <t>44 EU - 10 US</t>
+          <t>42 EU - 8.5 US</t>
         </is>
       </c>
       <c r="L25" s="15" t="inlineStr">
         <is>
-          <t>DM1602-100</t>
+          <t>DM7866-202</t>
         </is>
       </c>
       <c r="M25" s="15" t="inlineStr">
@@ -4144,28 +4144,32 @@
       <c r="P25" s="15" t="inlineStr"/>
       <c r="Q25" s="15" t="inlineStr">
         <is>
-          <t>juudith.rg@gmail.com</t>
+          <t>cristiancampos26500@gmail.com</t>
         </is>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
-          <t>Judith</t>
+          <t>Cristian</t>
         </is>
       </c>
       <c r="S25" s="15" t="inlineStr">
         <is>
-          <t>Robles Garcia</t>
-        </is>
-      </c>
-      <c r="T25" s="15" t="inlineStr"/>
+          <t>Campos Mata</t>
+        </is>
+      </c>
+      <c r="T25" s="15" t="inlineStr">
+        <is>
+          <t>+34632623867</t>
+        </is>
+      </c>
       <c r="U25" s="15" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #2)</t>
         </is>
       </c>
       <c r="V25" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W25" s="15" t="inlineStr">
@@ -4183,26 +4187,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>27.5</v>
+        <v>37.5</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>8.25</v>
+        <v>11.25</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>09/11/25 16:14</t>
+          <t>09/13/25 10:43</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6887025475925</t>
+          <t>78157</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4222,17 +4226,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Retro Low OG SP Travis Scott Velvet Brown</t>
+          <t>Dunk Low Off-White Lot 21</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>42 EU - 8.5 US</t>
+          <t>44 EU - 10 US</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>DM7866-202</t>
+          <t>DM1602-100</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -4253,32 +4257,28 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>cristiancampos26500@gmail.com</t>
+          <t>juudith.rg@gmail.com</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Cristian</t>
+          <t>Judith</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Campos Mata</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>+34632623867</t>
-        </is>
-      </c>
+          <t>Robles Garcia</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #2)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -4538,26 +4538,26 @@
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>Klarna Bank AB UK Branch</t>
+          <t>LINKGAINS PTE.LTD.</t>
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>153</v>
+        <v>335</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>7.65</v>
+        <v>16.75</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>2.3</v>
+        <v>5.03</v>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>09/10/25 09:03</t>
+          <t>09/09/25 17:32</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>77873</t>
+          <t>77821</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr">
@@ -4577,17 +4577,17 @@
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
-          <t>Air Force 1 Rope Laces</t>
+          <t>ASICS Gel-NYC Cream Arctic Sky</t>
         </is>
       </c>
       <c r="K29" s="15" t="inlineStr">
         <is>
-          <t>38 EU - 5.5 US</t>
+          <t>40 EU - 7 US</t>
         </is>
       </c>
       <c r="L29" s="15" t="inlineStr">
         <is>
-          <t>CW2288-111ME</t>
+          <t>1203A383-107</t>
         </is>
       </c>
       <c r="M29" s="15" t="inlineStr">
@@ -4608,17 +4608,17 @@
       <c r="P29" s="15" t="inlineStr"/>
       <c r="Q29" s="15" t="inlineStr">
         <is>
-          <t>kaaa-95@hotmail.com</t>
+          <t>gestoriapradillo@gmail.com</t>
         </is>
       </c>
       <c r="R29" s="15" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>LAURA</t>
         </is>
       </c>
       <c r="S29" s="15" t="inlineStr">
         <is>
-          <t>Serrano Sánchez</t>
+          <t>BORRAJO ROMERO</t>
         </is>
       </c>
       <c r="T29" s="15" t="inlineStr"/>
@@ -4634,16 +4634,24 @@
       </c>
       <c r="W29" s="15" t="inlineStr">
         <is>
-          <t>an unknown source</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="X29" s="15" t="inlineStr">
         <is>
-          <t>webgains</t>
-        </is>
-      </c>
-      <c r="Y29" s="15" t="inlineStr"/>
-      <c r="Z29" s="15" t="inlineStr"/>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="Y29" s="15" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="Z29" s="15" t="inlineStr">
+        <is>
+          <t>21366334315</t>
+        </is>
+      </c>
       <c r="AA29" s="15" t="inlineStr"/>
       <c r="AB29" s="15" t="inlineStr"/>
       <c r="AC29" s="15" t="inlineStr"/>
@@ -4651,26 +4659,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LINKGAINS PTE.LTD.</t>
+          <t>Klarna Bank AB UK Branch</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>335</v>
+        <v>153</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>16.75</v>
+        <v>7.65</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>5.03</v>
+        <v>2.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>09/09/25 17:32</t>
+          <t>09/10/25 09:03</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>77821</t>
+          <t>77873</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4690,17 +4698,17 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>ASICS Gel-NYC Cream Arctic Sky</t>
+          <t>Air Force 1 Rope Laces</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>40 EU - 7 US</t>
+          <t>38 EU - 5.5 US</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1203A383-107</t>
+          <t>CW2288-111ME</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -4721,17 +4729,17 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>gestoriapradillo@gmail.com</t>
+          <t>kaaa-95@hotmail.com</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>LAURA</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>BORRAJO ROMERO</t>
+          <t>Serrano Sánchez</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -4747,24 +4755,16 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>an unknown source</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>21366334315</t>
-        </is>
-      </c>
+          <t>webgains</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
@@ -4897,26 +4897,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Webravo SRL</t>
+          <t>Shoparize</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>09/09/25 14:38</t>
+          <t>09/09/25 01:55</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>77790</t>
+          <t>77760</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4936,17 +4936,17 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Adidas SL 72 OG Maroon Preloved Brown</t>
+          <t>Adidas SL 72 RS Black Carbon</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>41.3 EU - 8 US</t>
+          <t>44 EU - 10 US</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>IE3425</t>
+          <t>JH5098</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4967,20 +4967,24 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>portella.marina@gmail.com</t>
+          <t>manuelopez.mlg@gmail.com</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Marina</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Portella</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>López Garrido</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>+34673369013</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>First Order</t>
@@ -4993,10 +4997,14 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr"/>
+          <t>an unknown source</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>webgains</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
@@ -5006,26 +5014,26 @@
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>Shoparize</t>
+          <t>Webravo SRL</t>
         </is>
       </c>
       <c r="B33" s="16" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C33" s="16" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="D33" s="16" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>09/09/25 01:55</t>
+          <t>09/09/25 14:38</t>
         </is>
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>77760</t>
+          <t>77790</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
@@ -5045,17 +5053,17 @@
       </c>
       <c r="J33" s="15" t="inlineStr">
         <is>
-          <t>Adidas SL 72 RS Black Carbon</t>
+          <t>Adidas SL 72 OG Maroon Preloved Brown</t>
         </is>
       </c>
       <c r="K33" s="15" t="inlineStr">
         <is>
-          <t>44 EU - 10 US</t>
+          <t>41.3 EU - 8 US</t>
         </is>
       </c>
       <c r="L33" s="15" t="inlineStr">
         <is>
-          <t>JH5098</t>
+          <t>IE3425</t>
         </is>
       </c>
       <c r="M33" s="15" t="inlineStr">
@@ -5076,24 +5084,20 @@
       <c r="P33" s="15" t="inlineStr"/>
       <c r="Q33" s="15" t="inlineStr">
         <is>
-          <t>manuelopez.mlg@gmail.com</t>
+          <t>portella.marina@gmail.com</t>
         </is>
       </c>
       <c r="R33" s="15" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Marina</t>
         </is>
       </c>
       <c r="S33" s="15" t="inlineStr">
         <is>
-          <t>López Garrido</t>
-        </is>
-      </c>
-      <c r="T33" s="15" t="inlineStr">
-        <is>
-          <t>+34673369013</t>
-        </is>
-      </c>
+          <t>Portella</t>
+        </is>
+      </c>
+      <c r="T33" s="15" t="inlineStr"/>
       <c r="U33" s="15" t="inlineStr">
         <is>
           <t>First Order</t>
@@ -5106,14 +5110,10 @@
       </c>
       <c r="W33" s="15" t="inlineStr">
         <is>
-          <t>an unknown source</t>
-        </is>
-      </c>
-      <c r="X33" s="15" t="inlineStr">
-        <is>
-          <t>webgains</t>
-        </is>
-      </c>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="X33" s="15" t="inlineStr"/>
       <c r="Y33" s="15" t="inlineStr"/>
       <c r="Z33" s="15" t="inlineStr"/>
       <c r="AA33" s="15" t="inlineStr"/>
@@ -5236,26 +5236,26 @@
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>LINKGAINS PTE.LTD.</t>
+          <t>LINKPREFER LIMITED</t>
         </is>
       </c>
       <c r="B35" s="16" t="n">
-        <v>90</v>
+        <v>280</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>5.4</v>
+        <v>16.8</v>
       </c>
       <c r="D35" s="16" t="n">
-        <v>1.62</v>
+        <v>5.04</v>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>09/07/25 15:51</t>
+          <t>09/07/25 15:13</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>77615</t>
+          <t>77607</t>
         </is>
       </c>
       <c r="G35" s="15" t="inlineStr">
@@ -5275,17 +5275,17 @@
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
-          <t>Puma Arizona Zebra</t>
+          <t>Adidas Gazelle Indoor Bad Bunny Cabo Rojo</t>
         </is>
       </c>
       <c r="K35" s="15" t="inlineStr">
         <is>
-          <t>37 EU - 5 US</t>
+          <t>38.6 EU - 6 US</t>
         </is>
       </c>
       <c r="L35" s="15" t="inlineStr">
         <is>
-          <t>404398-01</t>
+          <t>JS5052</t>
         </is>
       </c>
       <c r="M35" s="15" t="inlineStr">
@@ -5306,69 +5306,89 @@
       <c r="P35" s="15" t="inlineStr"/>
       <c r="Q35" s="15" t="inlineStr">
         <is>
-          <t>jessijuan2014@gmail.com</t>
+          <t>browses.owners-8u@icloud.com</t>
         </is>
       </c>
       <c r="R35" s="15" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="S35" s="15" t="inlineStr">
         <is>
-          <t>Llopis</t>
+          <t>Schweitzer</t>
         </is>
       </c>
       <c r="T35" s="15" t="inlineStr">
         <is>
-          <t>+34650397617</t>
+          <t>+34680952342</t>
         </is>
       </c>
       <c r="U35" s="15" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #3)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="V35" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W35" s="15" t="inlineStr">
         <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="X35" s="15" t="inlineStr"/>
-      <c r="Y35" s="15" t="inlineStr"/>
-      <c r="Z35" s="15" t="inlineStr"/>
-      <c r="AA35" s="15" t="inlineStr"/>
-      <c r="AB35" s="15" t="inlineStr"/>
+          <t>an unknown source</t>
+        </is>
+      </c>
+      <c r="X35" s="15" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="Y35" s="15" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="Z35" s="15" t="inlineStr">
+        <is>
+          <t>CAMPAÑA_ESCALADO_AD</t>
+        </is>
+      </c>
+      <c r="AA35" s="15" t="inlineStr">
+        <is>
+          <t>120206246202400135</t>
+        </is>
+      </c>
+      <c r="AB35" s="15" t="inlineStr">
+        <is>
+          <t>120231190735490135</t>
+        </is>
+      </c>
       <c r="AC35" s="15" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LINKPREFER LIMITED</t>
+          <t>LINKGAINS PTE.LTD.</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>280</v>
+        <v>90</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>16.8</v>
+        <v>5.4</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>5.04</v>
+        <v>1.62</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>09/07/25 15:13</t>
+          <t>09/07/25 15:51</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>77607</t>
+          <t>77615</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5388,17 +5408,17 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Adidas Gazelle Indoor Bad Bunny Cabo Rojo</t>
+          <t>Puma Arizona Zebra</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>38.6 EU - 6 US</t>
+          <t>37 EU - 5 US</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>JS5052</t>
+          <t>404398-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -5419,64 +5439,44 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>browses.owners-8u@icloud.com</t>
+          <t>jessijuan2014@gmail.com</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Schweitzer</t>
+          <t>Llopis</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>+34680952342</t>
+          <t>+34650397617</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #3)</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>an unknown source</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>CAMPAÑA_ESCALADO_AD</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>120206246202400135</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>120231190735490135</t>
-        </is>
-      </c>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -5817,7 +5817,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Purplee Corp</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>09/05/25 20:13</t>
+          <t>09/02/25 21:53</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>77431</t>
+          <t>6870936355157</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>43 EU - 10 US</t>
+          <t>41 EU - 8.5 US</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -5887,22 +5887,22 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>pj_sanchez17@yahoo.es</t>
+          <t>sandrafresita@live.com</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Sanchez fernandez</t>
+          <t>Sáez badia</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>+34655472907</t>
+          <t>+34660229457</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="X40" t="inlineStr"/>
@@ -5930,26 +5930,26 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
+          <t>Invoke AB</t>
         </is>
       </c>
       <c r="B41" s="16" t="n">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="C41" s="16" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D41" s="16" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>09/02/25 21:53</t>
+          <t>09/04/25 19:12</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
         <is>
-          <t>6870936355157</t>
+          <t>77301</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr">
@@ -5969,17 +5969,17 @@
       </c>
       <c r="J41" s="15" t="inlineStr">
         <is>
-          <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
+          <t>Air Jordan 3 Retro Black Cat</t>
         </is>
       </c>
       <c r="K41" s="15" t="inlineStr">
         <is>
-          <t>41 EU - 8.5 US</t>
+          <t>41 EU - 8 US</t>
         </is>
       </c>
       <c r="L41" s="15" t="inlineStr">
         <is>
-          <t>310864-01</t>
+          <t>CT8532-001</t>
         </is>
       </c>
       <c r="M41" s="15" t="inlineStr">
@@ -6000,22 +6000,22 @@
       <c r="P41" s="15" t="inlineStr"/>
       <c r="Q41" s="15" t="inlineStr">
         <is>
-          <t>sandrafresita@live.com</t>
+          <t>alexitomendo1960@gmail.com</t>
         </is>
       </c>
       <c r="R41" s="15" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="S41" s="15" t="inlineStr">
         <is>
-          <t>Sáez badia</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="T41" s="15" t="inlineStr">
         <is>
-          <t>+34660229457</t>
+          <t>+34634868685</t>
         </is>
       </c>
       <c r="U41" s="15" t="inlineStr">
@@ -6030,10 +6030,14 @@
       </c>
       <c r="W41" s="15" t="inlineStr">
         <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="X41" s="15" t="inlineStr"/>
+          <t>an unknown source</t>
+        </is>
+      </c>
+      <c r="X41" s="15" t="inlineStr">
+        <is>
+          <t>webgains</t>
+        </is>
+      </c>
       <c r="Y41" s="15" t="inlineStr"/>
       <c r="Z41" s="15" t="inlineStr"/>
       <c r="AA41" s="15" t="inlineStr"/>
@@ -6043,26 +6047,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>09/04/25 19:12</t>
+          <t>09/05/25 20:13</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>77301</t>
+          <t>77431</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6082,17 +6086,17 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Air Jordan 3 Retro Black Cat</t>
+          <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>41 EU - 8 US</t>
+          <t>43 EU - 10 US</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CT8532-001</t>
+          <t>310864-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -6113,22 +6117,22 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>alexitomendo1960@gmail.com</t>
+          <t>pj_sanchez17@yahoo.es</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Sanchez fernandez</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>+34634868685</t>
+          <t>+34655472907</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6143,14 +6147,10 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>an unknown source</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>webgains</t>
-        </is>
-      </c>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
@@ -6160,56 +6160,56 @@
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Skimbit LTD</t>
         </is>
       </c>
       <c r="B43" s="16" t="n">
-        <v>250</v>
+        <v>96</v>
       </c>
       <c r="C43" s="16" t="n">
-        <v>15</v>
+        <v>4.8</v>
       </c>
       <c r="D43" s="16" t="n">
-        <v>4.5</v>
+        <v>1.44</v>
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>09/04/25 16:31</t>
+          <t>09/02/25 15:23</t>
         </is>
       </c>
       <c r="F43" s="15" t="inlineStr">
         <is>
-          <t>77278</t>
+          <t>77081</t>
         </is>
       </c>
       <c r="G43" s="15" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="H43" s="15" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I43" s="17" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="J43" s="15" t="inlineStr">
         <is>
-          <t>Air Jordan 3 Retro Pure Money</t>
+          <t>Adidas Campus 00s Grey White</t>
         </is>
       </c>
       <c r="K43" s="15" t="inlineStr">
         <is>
-          <t>41 EU - 8 US</t>
+          <t>42 EU - 8.5 US</t>
         </is>
       </c>
       <c r="L43" s="15" t="inlineStr">
         <is>
-          <t>CT8532-111</t>
+          <t>HQ8707</t>
         </is>
       </c>
       <c r="M43" s="15" t="inlineStr">
@@ -6230,40 +6230,44 @@
       <c r="P43" s="15" t="inlineStr"/>
       <c r="Q43" s="15" t="inlineStr">
         <is>
-          <t>sebastiancalvovinasco076@gmail.com</t>
+          <t>noapataly1602@gmail.com</t>
         </is>
       </c>
       <c r="R43" s="15" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="S43" s="15" t="inlineStr">
         <is>
-          <t>Calvo vinasco</t>
+          <t>Da Silva</t>
         </is>
       </c>
       <c r="T43" s="15" t="inlineStr">
         <is>
-          <t>+34655364031</t>
+          <t>+32490401121</t>
         </is>
       </c>
       <c r="U43" s="15" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #2)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="V43" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W43" s="15" t="inlineStr">
         <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="X43" s="15" t="inlineStr"/>
+          <t>an unknown source</t>
+        </is>
+      </c>
+      <c r="X43" s="15" t="inlineStr">
+        <is>
+          <t>chatgpt.com</t>
+        </is>
+      </c>
       <c r="Y43" s="15" t="inlineStr"/>
       <c r="Z43" s="15" t="inlineStr"/>
       <c r="AA43" s="15" t="inlineStr"/>
@@ -6273,56 +6277,56 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Skimbit LTD</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>96</v>
+        <v>250</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>4.8</v>
+        <v>15</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>1.44</v>
+        <v>4.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>09/02/25 15:23</t>
+          <t>09/04/25 16:31</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>77081</t>
+          <t>77278</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Adidas Campus 00s Grey White</t>
+          <t>Air Jordan 3 Retro Pure Money</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>42 EU - 8.5 US</t>
+          <t>41 EU - 8 US</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>HQ8707</t>
+          <t>CT8532-111</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -6343,44 +6347,40 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>noapataly1602@gmail.com</t>
+          <t>sebastiancalvovinasco076@gmail.com</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Patricia</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Da Silva</t>
+          <t>Calvo vinasco</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>+32490401121</t>
+          <t>+34655364031</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #2)</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>an unknown source</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>chatgpt.com</t>
-        </is>
-      </c>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
@@ -6708,22 +6708,22 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>127.5</v>
+        <v>70</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>7.65</v>
+        <v>4.2</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09/30/25 16:25</t>
+          <t>09/30/25 12:49</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>79375</t>
+          <t>79361</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6745,26 +6745,26 @@
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
+          <t>Mathias Kraft</t>
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="C3" s="16" t="n">
-        <v>4.2</v>
+        <v>10.8</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>1.26</v>
+        <v>3.24</v>
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>09/30/25 12:49</t>
+          <t>09/30/25 15:30</t>
         </is>
       </c>
       <c r="F3" s="15" t="inlineStr">
         <is>
-          <t>79361</t>
+          <t>79365</t>
         </is>
       </c>
       <c r="G3" s="15" t="inlineStr">
@@ -6786,26 +6786,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mathias Kraft</t>
+          <t>Digital Expand</t>
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>180</v>
+        <v>127.5</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>10.8</v>
+        <v>7.65</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>3.24</v>
+        <v>2.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>09/30/25 15:30</t>
+          <t>09/30/25 16:25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>79365</t>
+          <t>79375</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6950,31 +6950,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Webravo SRL</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>330</v>
+        <v>110</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>19.8</v>
+        <v>6.6</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>5.94</v>
+        <v>1.98</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>09/24/25 14:24</t>
+          <t>09/22/25 20:03</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>78891</t>
+          <t>78812</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7073,31 +7073,31 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Webravo SRL</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>110</v>
+        <v>330</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>6.6</v>
+        <v>19.8</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>1.98</v>
+        <v>5.94</v>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>09/22/25 20:03</t>
+          <t>09/24/25 14:24</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>78812</t>
+          <t>78891</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
@@ -7114,26 +7114,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
+          <t>Invoke AB</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>170</v>
+        <v>350</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>10.2</v>
+        <v>21</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>3.06</v>
+        <v>6.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>09/22/25 14:45</t>
+          <t>09/20/25 11:34</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6903116824917</t>
+          <t>6900010221909</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7155,26 +7155,26 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
+          <t>Purplee Corp</t>
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>6</v>
+        <v>10.2</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>1.8</v>
+        <v>3.06</v>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>09/18/25 19:39</t>
+          <t>09/22/25 14:45</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>6897694179669</t>
+          <t>6903116824917</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -7184,38 +7184,38 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
+          <t>Digital Expand</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>6.3</v>
+        <v>1.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>09/20/25 11:34</t>
+          <t>09/18/25 19:39</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6900010221909</t>
+          <t>6897694179669</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7225,38 +7225,38 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Pashion.dk ApS</t>
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>1.98</v>
+        <v>4.2</v>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>09/19/25 23:39</t>
+          <t>09/16/25 20:51</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>78602</t>
+          <t>6894848966997</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
@@ -7266,38 +7266,38 @@
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Webravo SRL</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>09/20/25 11:53</t>
+          <t>09/19/25 23:39</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>78608</t>
+          <t>78602</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7319,26 +7319,26 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Pashion.dk ApS</t>
+          <t>Webravo SRL</t>
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>280</v>
+        <v>90</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>09/16/25 20:51</t>
+          <t>09/20/25 11:53</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>6894848966997</t>
+          <t>78608</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
@@ -7401,26 +7401,26 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Pashion.dk ApS</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>6</v>
+        <v>5.28</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>09/16/25 16:05</t>
+          <t>09/15/25 11:50</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>78437</t>
+          <t>78383</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
@@ -7430,12 +7430,12 @@
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
@@ -7483,26 +7483,26 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Pashion.dk ApS</t>
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>5.28</v>
+        <v>6</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>09/15/25 11:50</t>
+          <t>09/16/25 16:05</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>78383</t>
+          <t>78437</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -7512,38 +7512,38 @@
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pashion.dk ApS</t>
+          <t>Purplee Corp</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>120</v>
+        <v>82.5</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>6</v>
+        <v>4.95</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>09/15/25 11:46</t>
+          <t>09/14/25 12:50</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>78382</t>
+          <t>6891134681429</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7553,38 +7553,38 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Pashion.dk ApS</t>
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>5.76</v>
+        <v>6</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>09/14/25 22:07</t>
+          <t>09/15/25 11:46</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>78374</t>
+          <t>78382</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
@@ -7594,38 +7594,38 @@
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>82.5</v>
+        <v>96</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>4.95</v>
+        <v>5.76</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>09/14/25 12:50</t>
+          <t>09/14/25 22:07</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6891134681429</t>
+          <t>78374</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7647,26 +7647,26 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Digital Expand</t>
         </is>
       </c>
       <c r="B25" s="16" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>37.5</v>
+        <v>27.5</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>11.25</v>
+        <v>8.25</v>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>09/13/25 10:43</t>
+          <t>09/11/25 16:14</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>78157</t>
+          <t>6887025475925</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -7688,26 +7688,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>27.5</v>
+        <v>37.5</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>8.25</v>
+        <v>11.25</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>09/11/25 16:14</t>
+          <t>09/13/25 10:43</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6887025475925</t>
+          <t>78157</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7811,26 +7811,26 @@
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>Klarna Bank AB UK Branch</t>
+          <t>LINKGAINS PTE.LTD.</t>
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>153</v>
+        <v>335</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>7.65</v>
+        <v>16.75</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>2.3</v>
+        <v>5.03</v>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>09/10/25 09:03</t>
+          <t>09/09/25 17:32</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>77873</t>
+          <t>77821</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr">
@@ -7852,26 +7852,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LINKGAINS PTE.LTD.</t>
+          <t>Klarna Bank AB UK Branch</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>335</v>
+        <v>153</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>16.75</v>
+        <v>7.65</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>5.03</v>
+        <v>2.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>09/09/25 17:32</t>
+          <t>09/10/25 09:03</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>77821</t>
+          <t>77873</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7934,26 +7934,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Webravo SRL</t>
+          <t>Shoparize</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>09/09/25 14:38</t>
+          <t>09/09/25 01:55</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>77790</t>
+          <t>77760</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7975,26 +7975,26 @@
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>Shoparize</t>
+          <t>Webravo SRL</t>
         </is>
       </c>
       <c r="B33" s="16" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C33" s="16" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="D33" s="16" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>09/09/25 01:55</t>
+          <t>09/09/25 14:38</t>
         </is>
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>77760</t>
+          <t>77790</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
@@ -8057,26 +8057,26 @@
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>LINKGAINS PTE.LTD.</t>
+          <t>LINKPREFER LIMITED</t>
         </is>
       </c>
       <c r="B35" s="16" t="n">
-        <v>90</v>
+        <v>280</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>5.4</v>
+        <v>16.8</v>
       </c>
       <c r="D35" s="16" t="n">
-        <v>1.62</v>
+        <v>5.04</v>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>09/07/25 15:51</t>
+          <t>09/07/25 15:13</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>77615</t>
+          <t>77607</t>
         </is>
       </c>
       <c r="G35" s="15" t="inlineStr">
@@ -8098,26 +8098,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LINKPREFER LIMITED</t>
+          <t>LINKGAINS PTE.LTD.</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>280</v>
+        <v>90</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>16.8</v>
+        <v>5.4</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>5.04</v>
+        <v>1.62</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>09/07/25 15:13</t>
+          <t>09/07/25 15:51</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>77607</t>
+          <t>77615</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -8262,7 +8262,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Purplee Corp</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>09/05/25 20:13</t>
+          <t>09/02/25 21:53</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>77431</t>
+          <t>6870936355157</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -8303,26 +8303,26 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
+          <t>Invoke AB</t>
         </is>
       </c>
       <c r="B41" s="16" t="n">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="C41" s="16" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D41" s="16" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>09/02/25 21:53</t>
+          <t>09/04/25 19:12</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
         <is>
-          <t>6870936355157</t>
+          <t>77301</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr">
@@ -8344,26 +8344,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>09/04/25 19:12</t>
+          <t>09/05/25 20:13</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>77301</t>
+          <t>77431</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -8385,82 +8385,82 @@
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
+          <t>Skimbit LTD</t>
         </is>
       </c>
       <c r="B43" s="16" t="n">
-        <v>250</v>
+        <v>96</v>
       </c>
       <c r="C43" s="16" t="n">
-        <v>15</v>
+        <v>4.8</v>
       </c>
       <c r="D43" s="16" t="n">
-        <v>4.5</v>
+        <v>1.44</v>
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>09/04/25 16:31</t>
+          <t>09/02/25 15:23</t>
         </is>
       </c>
       <c r="F43" s="15" t="inlineStr">
         <is>
-          <t>77278</t>
+          <t>77081</t>
         </is>
       </c>
       <c r="G43" s="15" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="H43" s="15" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Reventa</t>
         </is>
       </c>
       <c r="I43" s="17" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Skimbit LTD</t>
+          <t>BlueVision Interactive Limited</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>96</v>
+        <v>250</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>4.8</v>
+        <v>15</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>1.44</v>
+        <v>4.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>09/02/25 15:23</t>
+          <t>09/04/25 16:31</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>77081</t>
+          <t>77278</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>

--- a/scripts/generate_report_from_webgains/enriched_webgains_reports/Transacciones_newcop_2509_enriched.xlsx
+++ b/scripts/generate_report_from_webgains/enriched_webgains_reports/Transacciones_newcop_2509_enriched.xlsx
@@ -157,14 +157,14 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="8" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -696,26 +696,26 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>51.11%</t>
+          <t>70.21%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Reventa</t>
+          <t>Resell</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>48.89%</t>
+          <t>29.79%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>75.56%</t>
+          <t>73.33%</t>
         </is>
       </c>
     </row>
@@ -780,11 +780,11 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>24.44%</t>
+          <t>26.67%</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dunk Low Cacao Wow</t>
+          <t>Puma Arizona SD Flat Bronze-Alpine Snow</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
@@ -995,7 +995,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Dunk Low Grey Fog</t>
+          <t>Adidas Adizero Evo SL White Pure Teal</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
@@ -1010,7 +1010,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Puma Arizona SD Flat Bronze-Alpine Snow</t>
+          <t>Dunk Low Cacao Wow</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
@@ -1025,7 +1025,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Adidas Response CL Bad Bunny Paso Fino</t>
+          <t>Dunk Low Grey Fog</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
@@ -1040,7 +1040,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nike Zoom Vomero 5 Light Orewood Brown</t>
+          <t>Adidas Response CL Bad Bunny Paso Fino</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
@@ -1055,7 +1055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Adidas Adizero Evo SL White Pure Teal</t>
+          <t>Nike Zoom Vomero 5 Light Orewood Brown</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
@@ -1464,488 +1464,488 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Digital Expand</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="C2" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D2" s="14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>09/30/25 12:49</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>79361</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I2" s="15" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Puma Arizona SD Flat Bronze-Alpine Snow</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>37 EU - 5 US</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>402362-04</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>sandra.isla.88@gmail.com</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Isla</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>First Order</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Digital Expand</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>09/30/25 16:25</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>79375</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>Adidas Adizero Evo SL White Pure Teal</t>
+        </is>
+      </c>
+      <c r="K3" s="16" t="inlineStr">
+        <is>
+          <t>42 EU - 8.5 US</t>
+        </is>
+      </c>
+      <c r="L3" s="16" t="inlineStr">
+        <is>
+          <t>JS4487</t>
+        </is>
+      </c>
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="N3" s="16" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O3" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P3" s="16" t="inlineStr"/>
+      <c r="Q3" s="16" t="inlineStr"/>
+      <c r="R3" s="16" t="inlineStr"/>
+      <c r="S3" s="16" t="inlineStr"/>
+      <c r="T3" s="16" t="inlineStr">
+        <is>
+          <t>protomela@yahoo.es</t>
+        </is>
+      </c>
+      <c r="U3" s="16" t="inlineStr">
+        <is>
+          <t>Jose luis</t>
+        </is>
+      </c>
+      <c r="V3" s="16" t="inlineStr">
+        <is>
+          <t>Sanchis mañanos</t>
+        </is>
+      </c>
+      <c r="W3" s="16" t="inlineStr">
+        <is>
+          <t>+34671639303</t>
+        </is>
+      </c>
+      <c r="X3" s="16" t="inlineStr">
+        <is>
+          <t>First Order</t>
+        </is>
+      </c>
+      <c r="Y3" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z3" s="16" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="AA3" s="16" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="AB3" s="16" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="AC3" s="16" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
+      <c r="AD3" s="16" t="inlineStr"/>
+      <c r="AE3" s="16" t="inlineStr"/>
+      <c r="AF3" s="16" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Skimbit LTD</t>
         </is>
       </c>
-      <c r="B2" s="15" t="n">
+      <c r="B4" s="20" t="n">
         <v>429</v>
       </c>
-      <c r="C2" s="15" t="n">
+      <c r="C4" s="20" t="n">
         <v>22.44</v>
       </c>
-      <c r="D2" s="15" t="n">
+      <c r="D4" s="20" t="n">
         <v>6.73</v>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>09/30/25 21:03</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>79415</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="I4" s="21" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="J2" s="14" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>Puma Speedcat Wine Club Wns Brown, Dunk Low Cacao Wow, Dunk Low Grey Fog</t>
         </is>
       </c>
-      <c r="K2" s="14" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>40 EU - 7.5 US, 43 EU - 11 US, 43 EU - 9.5 US</t>
         </is>
       </c>
-      <c r="L2" s="14" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>402562-01, DD1503-124, DD1391-103</t>
         </is>
       </c>
-      <c r="M2" s="14" t="inlineStr">
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="N2" s="14" t="inlineStr">
+      <c r="N4" s="19" t="inlineStr">
         <is>
           <t>UNFULFILLED</t>
         </is>
       </c>
-      <c r="O2" s="14" t="inlineStr">
+      <c r="O4" s="19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P2" s="14" t="inlineStr">
+      <c r="P4" s="19" t="inlineStr">
         <is>
           <t>CANCELLED</t>
         </is>
       </c>
-      <c r="Q2" s="14" t="inlineStr"/>
-      <c r="R2" s="14" t="inlineStr"/>
-      <c r="S2" s="14" t="inlineStr">
+      <c r="Q4" s="19" t="inlineStr"/>
+      <c r="R4" s="19" t="inlineStr"/>
+      <c r="S4" s="19" t="inlineStr">
         <is>
           <t>PEDIDO NO PREPARADO</t>
         </is>
       </c>
-      <c r="T2" s="14" t="inlineStr">
+      <c r="T4" s="19" t="inlineStr">
         <is>
           <t>aitirvicente110397@gmail.com</t>
         </is>
       </c>
-      <c r="U2" s="14" t="inlineStr">
+      <c r="U4" s="19" t="inlineStr">
         <is>
           <t>Asier</t>
         </is>
       </c>
-      <c r="V2" s="14" t="inlineStr">
+      <c r="V4" s="19" t="inlineStr">
         <is>
           <t>Vicente de diego</t>
         </is>
       </c>
-      <c r="W2" s="14" t="inlineStr"/>
-      <c r="X2" s="14" t="inlineStr">
+      <c r="W4" s="19" t="inlineStr"/>
+      <c r="X4" s="19" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y2" s="14" t="inlineStr">
+      <c r="Y4" s="19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z2" s="14" t="inlineStr">
+      <c r="Z4" s="19" t="inlineStr">
         <is>
           <t>https://www.sequra.com/</t>
         </is>
       </c>
-      <c r="AA2" s="14" t="inlineStr"/>
-      <c r="AB2" s="14" t="inlineStr"/>
-      <c r="AC2" s="14" t="inlineStr"/>
-      <c r="AD2" s="14" t="inlineStr"/>
-      <c r="AE2" s="14" t="inlineStr"/>
-      <c r="AF2" s="14" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>Digital Expand</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="C3" s="18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D3" s="18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>09/30/25 12:49</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>79361</t>
-        </is>
-      </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="AA4" s="19" t="inlineStr"/>
+      <c r="AB4" s="19" t="inlineStr"/>
+      <c r="AC4" s="19" t="inlineStr"/>
+      <c r="AD4" s="19" t="inlineStr"/>
+      <c r="AE4" s="19" t="inlineStr"/>
+      <c r="AF4" s="19" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>BlueVision Interactive Limited</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>380</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>09/26/25 15:13</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>79025</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I3" s="19" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="J3" s="17" t="inlineStr">
-        <is>
-          <t>Puma Arizona SD Flat Bronze-Alpine Snow</t>
-        </is>
-      </c>
-      <c r="K3" s="17" t="inlineStr">
-        <is>
-          <t>37 EU - 5 US</t>
-        </is>
-      </c>
-      <c r="L3" s="17" t="inlineStr">
-        <is>
-          <t>402362-04</t>
-        </is>
-      </c>
-      <c r="M3" s="17" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>Adidas Response CL Bad Bunny Paso Fino, Nike Zoom Vomero 5 Light Orewood Brown</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>42.6 EU - 9 US, 43 EU - 9.5 US</t>
+        </is>
+      </c>
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t>ID0780, HF1553-100</t>
+        </is>
+      </c>
+      <c r="M5" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N5" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O3" s="17" t="inlineStr">
+      <c r="O5" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr"/>
-      <c r="Q3" s="17" t="inlineStr"/>
-      <c r="R3" s="17" t="inlineStr"/>
-      <c r="S3" s="17" t="inlineStr"/>
-      <c r="T3" s="17" t="inlineStr">
-        <is>
-          <t>sandra.isla.88@gmail.com</t>
-        </is>
-      </c>
-      <c r="U3" s="17" t="inlineStr">
-        <is>
-          <t>Sandra</t>
-        </is>
-      </c>
-      <c r="V3" s="17" t="inlineStr">
-        <is>
-          <t>Isla</t>
-        </is>
-      </c>
-      <c r="W3" s="17" t="inlineStr"/>
-      <c r="X3" s="17" t="inlineStr">
+      <c r="P5" s="16" t="inlineStr"/>
+      <c r="Q5" s="16" t="inlineStr"/>
+      <c r="R5" s="16" t="inlineStr"/>
+      <c r="S5" s="16" t="inlineStr"/>
+      <c r="T5" s="16" t="inlineStr">
+        <is>
+          <t>josesosalopez519@gmail.com</t>
+        </is>
+      </c>
+      <c r="U5" s="16" t="inlineStr">
+        <is>
+          <t>jose</t>
+        </is>
+      </c>
+      <c r="V5" s="16" t="inlineStr">
+        <is>
+          <t>lopez Sosa</t>
+        </is>
+      </c>
+      <c r="W5" s="16" t="inlineStr"/>
+      <c r="X5" s="16" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y3" s="17" t="inlineStr">
+      <c r="Y5" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z3" s="17" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="AA3" s="17" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="AB3" s="17" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="AC3" s="17" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
-      <c r="AD3" s="17" t="inlineStr"/>
-      <c r="AE3" s="17" t="inlineStr"/>
-      <c r="AF3" s="17" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BlueVision Interactive Limited</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="n">
-        <v>380</v>
-      </c>
-      <c r="C4" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="D4" s="20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>09/26/25 15:13</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>79025</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I4" s="21" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Adidas Response CL Bad Bunny Paso Fino, Nike Zoom Vomero 5 Light Orewood Brown</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>42.6 EU - 9 US, 43 EU - 9.5 US</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>ID0780, HF1553-100</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>FULFILLED</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>josesosalopez519@gmail.com</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>jose</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>lopez Sosa</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>First Order</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z5" s="16" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Digital Expand</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n">
-        <v>127.5</v>
-      </c>
-      <c r="C5" s="18" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="D5" s="18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>09/30/25 16:25</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>79375</t>
-        </is>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I5" s="19" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t>Adidas Adizero Evo SL White Pure Teal</t>
-        </is>
-      </c>
-      <c r="K5" s="17" t="inlineStr">
-        <is>
-          <t>42 EU - 8.5 US</t>
-        </is>
-      </c>
-      <c r="L5" s="17" t="inlineStr">
-        <is>
-          <t>JS4487</t>
-        </is>
-      </c>
-      <c r="M5" s="17" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
-      </c>
-      <c r="N5" s="17" t="inlineStr">
-        <is>
-          <t>FULFILLED</t>
-        </is>
-      </c>
-      <c r="O5" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P5" s="17" t="inlineStr"/>
-      <c r="Q5" s="17" t="inlineStr"/>
-      <c r="R5" s="17" t="inlineStr"/>
-      <c r="S5" s="17" t="inlineStr"/>
-      <c r="T5" s="17" t="inlineStr">
-        <is>
-          <t>protomela@yahoo.es</t>
-        </is>
-      </c>
-      <c r="U5" s="17" t="inlineStr">
-        <is>
-          <t>Jose luis</t>
-        </is>
-      </c>
-      <c r="V5" s="17" t="inlineStr">
-        <is>
-          <t>Sanchis mañanos</t>
-        </is>
-      </c>
-      <c r="W5" s="17" t="inlineStr">
-        <is>
-          <t>+34671639303</t>
-        </is>
-      </c>
-      <c r="X5" s="17" t="inlineStr">
-        <is>
-          <t>First Order</t>
-        </is>
-      </c>
-      <c r="Y5" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z5" s="17" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="AA5" s="17" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="AB5" s="17" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="AC5" s="17" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
-      <c r="AD5" s="17" t="inlineStr"/>
-      <c r="AE5" s="17" t="inlineStr"/>
-      <c r="AF5" s="17" t="inlineStr"/>
+      <c r="AA5" s="16" t="inlineStr"/>
+      <c r="AB5" s="16" t="inlineStr"/>
+      <c r="AC5" s="16" t="inlineStr"/>
+      <c r="AD5" s="16" t="inlineStr"/>
+      <c r="AE5" s="16" t="inlineStr"/>
+      <c r="AF5" s="16" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1953,13 +1953,13 @@
           <t>Mathias Kraft</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="14" t="n">
         <v>180</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="14" t="n">
         <v>10.8</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="14" t="n">
         <v>3.24</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -1982,7 +1982,7 @@
           <t>Retail</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -2064,116 +2064,128 @@
       <c r="AF6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>BlueVision Interactive Limited</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="n">
-        <v>330</v>
-      </c>
-      <c r="C7" s="18" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="D7" s="18" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>09/24/25 14:24</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>78891</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Webravo SRL</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>09/24/25 19:56</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>78931</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>Denim Tears The Cotton Wreath Sweatshirt Black</t>
-        </is>
-      </c>
-      <c r="K7" s="17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L7" s="17" t="inlineStr">
-        <is>
-          <t>DENIMBW</t>
-        </is>
-      </c>
-      <c r="M7" s="17" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>Adidas Samba OG Earth Strata Wonder White</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>39.3 EU - 6.5 US</t>
+        </is>
+      </c>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>JI3184</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O7" s="17" t="inlineStr">
+      <c r="O7" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr"/>
-      <c r="Q7" s="17" t="inlineStr"/>
-      <c r="R7" s="17" t="inlineStr"/>
-      <c r="S7" s="17" t="inlineStr"/>
-      <c r="T7" s="17" t="inlineStr">
-        <is>
-          <t>sandionisio7@gmail.com</t>
-        </is>
-      </c>
-      <c r="U7" s="17" t="inlineStr">
-        <is>
-          <t>Antonio</t>
-        </is>
-      </c>
-      <c r="V7" s="17" t="inlineStr">
-        <is>
-          <t>Neira Parra</t>
-        </is>
-      </c>
-      <c r="W7" s="17" t="inlineStr"/>
-      <c r="X7" s="17" t="inlineStr">
-        <is>
-          <t>Repeat Customer (Order #3)</t>
-        </is>
-      </c>
-      <c r="Y7" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z7" s="17" t="inlineStr">
+      <c r="P7" s="16" t="inlineStr"/>
+      <c r="Q7" s="16" t="inlineStr"/>
+      <c r="R7" s="16" t="inlineStr"/>
+      <c r="S7" s="16" t="inlineStr"/>
+      <c r="T7" s="16" t="inlineStr">
+        <is>
+          <t>anasrzz99@gmail.com</t>
+        </is>
+      </c>
+      <c r="U7" s="16" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="V7" s="16" t="inlineStr">
+        <is>
+          <t>Suárez Alcaraz</t>
+        </is>
+      </c>
+      <c r="W7" s="16" t="inlineStr"/>
+      <c r="X7" s="16" t="inlineStr">
+        <is>
+          <t>First Order</t>
+        </is>
+      </c>
+      <c r="Y7" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z7" s="16" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="AA7" s="17" t="inlineStr"/>
-      <c r="AB7" s="17" t="inlineStr"/>
-      <c r="AC7" s="17" t="inlineStr"/>
-      <c r="AD7" s="17" t="inlineStr"/>
-      <c r="AE7" s="17" t="inlineStr"/>
-      <c r="AF7" s="17" t="inlineStr"/>
+      <c r="AA7" s="16" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="AB7" s="16" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="AC7" s="16" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
+      <c r="AD7" s="16" t="inlineStr"/>
+      <c r="AE7" s="16" t="inlineStr"/>
+      <c r="AF7" s="16" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2181,23 +2193,23 @@
           <t>Webravo SRL</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
-        <v>96</v>
-      </c>
-      <c r="C8" s="20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="D8" s="20" t="n">
-        <v>1.44</v>
+      <c r="B8" s="14" t="n">
+        <v>170</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>2.55</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>09/24/25 19:56</t>
+          <t>09/24/25 10:57</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>78931</t>
+          <t>78876</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2210,24 +2222,24 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Adidas Samba OG Earth Strata Wonder White</t>
+          <t>Essentials Hoodie (FW22) Light Oatmeal, Essentials Hoodie (FW22) Light Oatmeal</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>39.3 EU - 6.5 US</t>
+          <t>M, S</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>JI3184</t>
+          <t>192SU224417F, 192SU224417F</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -2251,28 +2263,32 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>anasrzz99@gmail.com</t>
+          <t>ponsviladomat@hotmail.es</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Rosa</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Suárez Alcaraz</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr"/>
+          <t>Pons Viladomat</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>+34676934778</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #3)</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2300,128 +2316,116 @@
       <c r="AF8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>Webravo SRL</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="n">
-        <v>99</v>
-      </c>
-      <c r="C9" s="18" t="n">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>BlueVision Interactive Limited</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>330</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D9" s="17" t="n">
         <v>5.94</v>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>09/23/25 11:28</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>78821</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>09/24/25 14:24</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>78891</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>Puma Speedcat Wine Club Wns Brown</t>
-        </is>
-      </c>
-      <c r="K9" s="17" t="inlineStr">
-        <is>
-          <t>37 EU - 5 US</t>
-        </is>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>402562-01</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>Denim Tears The Cotton Wreath Sweatshirt Black</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>DENIMBW</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr"/>
-      <c r="Q9" s="17" t="inlineStr"/>
-      <c r="R9" s="17" t="inlineStr"/>
-      <c r="S9" s="17" t="inlineStr"/>
-      <c r="T9" s="17" t="inlineStr">
-        <is>
-          <t>lumarfer1462@gmail.com</t>
-        </is>
-      </c>
-      <c r="U9" s="17" t="inlineStr">
-        <is>
-          <t>Lucia</t>
-        </is>
-      </c>
-      <c r="V9" s="17" t="inlineStr">
-        <is>
-          <t>Martínez Fernández</t>
-        </is>
-      </c>
-      <c r="W9" s="17" t="inlineStr"/>
-      <c r="X9" s="17" t="inlineStr">
-        <is>
-          <t>First Order</t>
-        </is>
-      </c>
-      <c r="Y9" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z9" s="17" t="inlineStr">
+      <c r="P9" s="16" t="inlineStr"/>
+      <c r="Q9" s="16" t="inlineStr"/>
+      <c r="R9" s="16" t="inlineStr"/>
+      <c r="S9" s="16" t="inlineStr"/>
+      <c r="T9" s="16" t="inlineStr">
+        <is>
+          <t>sandionisio7@gmail.com</t>
+        </is>
+      </c>
+      <c r="U9" s="16" t="inlineStr">
+        <is>
+          <t>Antonio</t>
+        </is>
+      </c>
+      <c r="V9" s="16" t="inlineStr">
+        <is>
+          <t>Neira Parra</t>
+        </is>
+      </c>
+      <c r="W9" s="16" t="inlineStr"/>
+      <c r="X9" s="16" t="inlineStr">
+        <is>
+          <t>Repeat Customer (Order #3)</t>
+        </is>
+      </c>
+      <c r="Y9" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z9" s="16" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="AA9" s="17" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="AB9" s="17" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="AC9" s="17" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
-      <c r="AD9" s="17" t="inlineStr"/>
-      <c r="AE9" s="17" t="inlineStr"/>
-      <c r="AF9" s="17" t="inlineStr"/>
+      <c r="AA9" s="16" t="inlineStr"/>
+      <c r="AB9" s="16" t="inlineStr"/>
+      <c r="AC9" s="16" t="inlineStr"/>
+      <c r="AD9" s="16" t="inlineStr"/>
+      <c r="AE9" s="16" t="inlineStr"/>
+      <c r="AF9" s="16" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2429,23 +2433,23 @@
           <t>Webravo SRL</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
-        <v>170</v>
-      </c>
-      <c r="C10" s="20" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>2.55</v>
+      <c r="B10" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>1.78</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>09/24/25 10:57</t>
+          <t>09/23/25 11:28</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>78876</t>
+          <t>78821</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2455,27 +2459,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I10" s="21" t="inlineStr">
-        <is>
-          <t>5%</t>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>6%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Essentials Hoodie (FW22) Light Oatmeal, Essentials Hoodie (FW22) Light Oatmeal</t>
+          <t>Puma Speedcat Wine Club Wns Brown</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>M, S</t>
+          <t>37 EU - 5 US</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>192SU224417F, 192SU224417F</t>
+          <t>402562-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -2499,32 +2503,28 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
-          <t>ponsviladomat@hotmail.es</t>
+          <t>lumarfer1462@gmail.com</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Rosa</t>
+          <t>Lucia</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Pons Viladomat</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>+34676934778</t>
-        </is>
-      </c>
+          <t>Martínez Fernández</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #3)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2552,128 +2552,128 @@
       <c r="AF10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Webravo SRL</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="17" t="n">
         <v>110</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="17" t="n">
         <v>6.6</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="17" t="n">
         <v>1.98</v>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>09/22/25 20:03</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>78812</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>Adidas Samba OG Maroon Off White Gum</t>
         </is>
       </c>
-      <c r="K11" s="17" t="inlineStr">
+      <c r="K11" s="16" t="inlineStr">
         <is>
           <t>39.3 EU - 6.5 US</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="16" t="inlineStr">
         <is>
           <t>JR8844</t>
         </is>
       </c>
-      <c r="M11" s="17" t="inlineStr">
+      <c r="M11" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O11" s="17" t="inlineStr">
+      <c r="O11" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr"/>
-      <c r="Q11" s="17" t="inlineStr"/>
-      <c r="R11" s="17" t="inlineStr"/>
-      <c r="S11" s="17" t="inlineStr"/>
-      <c r="T11" s="17" t="inlineStr">
+      <c r="P11" s="16" t="inlineStr"/>
+      <c r="Q11" s="16" t="inlineStr"/>
+      <c r="R11" s="16" t="inlineStr"/>
+      <c r="S11" s="16" t="inlineStr"/>
+      <c r="T11" s="16" t="inlineStr">
         <is>
           <t>ccarbonell.torrees@gmail.com</t>
         </is>
       </c>
-      <c r="U11" s="17" t="inlineStr">
+      <c r="U11" s="16" t="inlineStr">
         <is>
           <t>Carlota</t>
         </is>
       </c>
-      <c r="V11" s="17" t="inlineStr">
+      <c r="V11" s="16" t="inlineStr">
         <is>
           <t>Carbonell Torres</t>
         </is>
       </c>
-      <c r="W11" s="17" t="inlineStr"/>
-      <c r="X11" s="17" t="inlineStr">
+      <c r="W11" s="16" t="inlineStr"/>
+      <c r="X11" s="16" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y11" s="17" t="inlineStr">
+      <c r="Y11" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z11" s="17" t="inlineStr">
+      <c r="Z11" s="16" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="AA11" s="17" t="inlineStr">
+      <c r="AA11" s="16" t="inlineStr">
         <is>
           <t>google</t>
         </is>
       </c>
-      <c r="AB11" s="17" t="inlineStr">
+      <c r="AB11" s="16" t="inlineStr">
         <is>
           <t>cpc</t>
         </is>
       </c>
-      <c r="AC11" s="17" t="inlineStr">
+      <c r="AC11" s="16" t="inlineStr">
         <is>
           <t>{campaignname}</t>
         </is>
       </c>
-      <c r="AD11" s="17" t="inlineStr"/>
-      <c r="AE11" s="17" t="inlineStr"/>
-      <c r="AF11" s="17" t="inlineStr"/>
+      <c r="AD11" s="16" t="inlineStr"/>
+      <c r="AE11" s="16" t="inlineStr"/>
+      <c r="AF11" s="16" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2681,13 +2681,13 @@
           <t>Purplee Corp</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="14" t="n">
         <v>170</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="14" t="n">
         <v>10.2</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="14" t="n">
         <v>3.06</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -2710,7 +2710,7 @@
           <t>Retail</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -2804,116 +2804,116 @@
       <c r="AF12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Invoke AB</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="17" t="n">
         <v>350</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="17" t="n">
         <v>6.3</v>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>09/20/25 11:34</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>6900010221909</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t>Air Jordan 4 Retro OG SP Undefeated</t>
         </is>
       </c>
-      <c r="K13" s="17" t="inlineStr">
+      <c r="K13" s="16" t="inlineStr">
         <is>
           <t>46 EU - 12 US</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t>IB1519-200</t>
         </is>
       </c>
-      <c r="M13" s="17" t="inlineStr">
+      <c r="M13" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O13" s="17" t="inlineStr">
+      <c r="O13" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr"/>
-      <c r="Q13" s="17" t="inlineStr"/>
-      <c r="R13" s="17" t="inlineStr"/>
-      <c r="S13" s="17" t="inlineStr"/>
-      <c r="T13" s="17" t="inlineStr">
+      <c r="P13" s="16" t="inlineStr"/>
+      <c r="Q13" s="16" t="inlineStr"/>
+      <c r="R13" s="16" t="inlineStr"/>
+      <c r="S13" s="16" t="inlineStr"/>
+      <c r="T13" s="16" t="inlineStr">
         <is>
           <t>blanco_negro1977@hotmail.com</t>
         </is>
       </c>
-      <c r="U13" s="17" t="inlineStr">
+      <c r="U13" s="16" t="inlineStr">
         <is>
           <t>Jorge</t>
         </is>
       </c>
-      <c r="V13" s="17" t="inlineStr">
+      <c r="V13" s="16" t="inlineStr">
         <is>
           <t>Lozano lozano</t>
         </is>
       </c>
-      <c r="W13" s="17" t="inlineStr">
+      <c r="W13" s="16" t="inlineStr">
         <is>
           <t>+34654624273</t>
         </is>
       </c>
-      <c r="X13" s="17" t="inlineStr">
+      <c r="X13" s="16" t="inlineStr">
         <is>
           <t>Repeat Customer (Order #4)</t>
         </is>
       </c>
-      <c r="Y13" s="17" t="inlineStr">
+      <c r="Y13" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Z13" s="17" t="inlineStr"/>
-      <c r="AA13" s="17" t="inlineStr"/>
-      <c r="AB13" s="17" t="inlineStr"/>
-      <c r="AC13" s="17" t="inlineStr"/>
-      <c r="AD13" s="17" t="inlineStr"/>
-      <c r="AE13" s="17" t="inlineStr"/>
-      <c r="AF13" s="17" t="inlineStr"/>
+      <c r="Z13" s="16" t="inlineStr"/>
+      <c r="AA13" s="16" t="inlineStr"/>
+      <c r="AB13" s="16" t="inlineStr"/>
+      <c r="AC13" s="16" t="inlineStr"/>
+      <c r="AD13" s="16" t="inlineStr"/>
+      <c r="AE13" s="16" t="inlineStr"/>
+      <c r="AF13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2921,13 +2921,13 @@
           <t>Digital Expand</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="14" t="n">
         <v>120</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="14" t="n">
         <v>1.8</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -2950,7 +2950,7 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -3028,152 +3028,152 @@
       <c r="AF14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Webravo SRL</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="17" t="n">
         <v>90</v>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="17" t="n">
         <v>5.4</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="17" t="n">
         <v>1.62</v>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>09/20/25 11:53</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>78608</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I15" s="19" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>Adidas Samba Jane Cream Black Gum</t>
         </is>
       </c>
-      <c r="K15" s="17" t="inlineStr">
+      <c r="K15" s="16" t="inlineStr">
         <is>
           <t>38 EU - 5.5 US</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="16" t="inlineStr">
         <is>
           <t>JR7338</t>
         </is>
       </c>
-      <c r="M15" s="17" t="inlineStr">
+      <c r="M15" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="N15" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O15" s="17" t="inlineStr">
+      <c r="O15" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P15" s="17" t="inlineStr"/>
-      <c r="Q15" s="17" t="inlineStr"/>
-      <c r="R15" s="17" t="inlineStr"/>
-      <c r="S15" s="17" t="inlineStr"/>
-      <c r="T15" s="17" t="inlineStr">
+      <c r="P15" s="16" t="inlineStr"/>
+      <c r="Q15" s="16" t="inlineStr"/>
+      <c r="R15" s="16" t="inlineStr"/>
+      <c r="S15" s="16" t="inlineStr"/>
+      <c r="T15" s="16" t="inlineStr">
         <is>
           <t>paulalopezpuyol12@gmail.com</t>
         </is>
       </c>
-      <c r="U15" s="17" t="inlineStr">
+      <c r="U15" s="16" t="inlineStr">
         <is>
           <t>Paula</t>
         </is>
       </c>
-      <c r="V15" s="17" t="inlineStr">
+      <c r="V15" s="16" t="inlineStr">
         <is>
           <t>López Puyol</t>
         </is>
       </c>
-      <c r="W15" s="17" t="inlineStr"/>
-      <c r="X15" s="17" t="inlineStr">
+      <c r="W15" s="16" t="inlineStr"/>
+      <c r="X15" s="16" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y15" s="17" t="inlineStr">
+      <c r="Y15" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z15" s="17" t="inlineStr">
+      <c r="Z15" s="16" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="AA15" s="17" t="inlineStr">
+      <c r="AA15" s="16" t="inlineStr">
         <is>
           <t>google</t>
         </is>
       </c>
-      <c r="AB15" s="17" t="inlineStr">
+      <c r="AB15" s="16" t="inlineStr">
         <is>
           <t>cpc</t>
         </is>
       </c>
-      <c r="AC15" s="17" t="inlineStr">
+      <c r="AC15" s="16" t="inlineStr">
         <is>
           <t>{campaignname}</t>
         </is>
       </c>
-      <c r="AD15" s="17" t="inlineStr"/>
-      <c r="AE15" s="17" t="inlineStr"/>
-      <c r="AF15" s="17" t="inlineStr"/>
+      <c r="AD15" s="16" t="inlineStr"/>
+      <c r="AE15" s="16" t="inlineStr"/>
+      <c r="AF15" s="16" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pashion.dk ApS</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="n">
-        <v>280</v>
-      </c>
-      <c r="C16" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="D16" s="20" t="n">
-        <v>4.2</v>
+          <t>BlueVision Interactive Limited</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>1.98</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>09/16/25 20:51</t>
+          <t>09/19/25 23:39</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6894848966997</t>
+          <t>78602</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3183,27 +3183,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>5%</t>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>6%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Air Jordan 3 Retro Black Cat</t>
+          <t>Adidas Samba OG Maroon Off White Gum</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>36.5 EU - 4.5 US</t>
+          <t>40.6 EU - 7.5 US</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CT8532-001</t>
+          <t>JR8844</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -3227,32 +3227,28 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>restauracionespablogarcia@hotmail.com</t>
+          <t>anamariamenzr1@hotmail.com</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Liaño cobo</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>+34699813897</t>
-        </is>
-      </c>
+          <t>Menezo Rojas</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #2)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -3260,178 +3256,194 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>{campaignname}</t>
+        </is>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>LINKGAINS PTE.LTD.</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="n">
-        <v>120</v>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>09/17/25 21:49</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>78504</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Pashion.dk ApS</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>280</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>09/16/25 20:51</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>6894848966997</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I17" s="19" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>44 EU - 10.5 US</t>
-        </is>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>310864-01</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="inlineStr">
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>Air Jordan 3 Retro Black Cat</t>
+        </is>
+      </c>
+      <c r="K17" s="16" t="inlineStr">
+        <is>
+          <t>36.5 EU - 4.5 US</t>
+        </is>
+      </c>
+      <c r="L17" s="16" t="inlineStr">
+        <is>
+          <t>CT8532-001</t>
+        </is>
+      </c>
+      <c r="M17" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="N17" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O17" s="17" t="inlineStr">
+      <c r="O17" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P17" s="17" t="inlineStr"/>
-      <c r="Q17" s="17" t="inlineStr"/>
-      <c r="R17" s="17" t="inlineStr"/>
-      <c r="S17" s="17" t="inlineStr"/>
-      <c r="T17" s="17" t="inlineStr">
-        <is>
-          <t>carrie.joris@gmail.com</t>
-        </is>
-      </c>
-      <c r="U17" s="17" t="inlineStr">
-        <is>
-          <t>Joris</t>
-        </is>
-      </c>
-      <c r="V17" s="17" t="inlineStr">
-        <is>
-          <t>Carrié</t>
-        </is>
-      </c>
-      <c r="W17" s="17" t="inlineStr"/>
-      <c r="X17" s="17" t="inlineStr">
-        <is>
-          <t>First Order</t>
-        </is>
-      </c>
-      <c r="Y17" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z17" s="17" t="inlineStr">
+      <c r="P17" s="16" t="inlineStr"/>
+      <c r="Q17" s="16" t="inlineStr"/>
+      <c r="R17" s="16" t="inlineStr"/>
+      <c r="S17" s="16" t="inlineStr"/>
+      <c r="T17" s="16" t="inlineStr">
+        <is>
+          <t>restauracionespablogarcia@hotmail.com</t>
+        </is>
+      </c>
+      <c r="U17" s="16" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="V17" s="16" t="inlineStr">
+        <is>
+          <t>Liaño cobo</t>
+        </is>
+      </c>
+      <c r="W17" s="16" t="inlineStr">
+        <is>
+          <t>+34699813897</t>
+        </is>
+      </c>
+      <c r="X17" s="16" t="inlineStr">
+        <is>
+          <t>Repeat Customer (Order #2)</t>
+        </is>
+      </c>
+      <c r="Y17" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z17" s="16" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="AA17" s="17" t="inlineStr"/>
-      <c r="AB17" s="17" t="inlineStr"/>
-      <c r="AC17" s="17" t="inlineStr"/>
-      <c r="AD17" s="17" t="inlineStr"/>
-      <c r="AE17" s="17" t="inlineStr"/>
-      <c r="AF17" s="17" t="inlineStr"/>
+      <c r="AA17" s="16" t="inlineStr"/>
+      <c r="AB17" s="16" t="inlineStr"/>
+      <c r="AC17" s="16" t="inlineStr"/>
+      <c r="AD17" s="16" t="inlineStr"/>
+      <c r="AE17" s="16" t="inlineStr"/>
+      <c r="AF17" s="16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="n">
-        <v>110</v>
-      </c>
-      <c r="C18" s="20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="D18" s="20" t="n">
-        <v>1.98</v>
+          <t>LINKGAINS PTE.LTD.</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>1.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>09/19/25 23:39</t>
+          <t>09/17/25 21:49</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>78602</t>
+          <t>78504</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>6%</t>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>5%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Adidas Samba OG Maroon Off White Gum</t>
+          <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>40.6 EU - 7.5 US</t>
+          <t>44 EU - 10.5 US</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>JR8844</t>
+          <t>310864-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3455,17 +3467,17 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>anamariamenzr1@hotmail.com</t>
+          <t>carrie.joris@gmail.com</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Joris</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Menezo Rojas</t>
+          <t>Carrié</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -3484,176 +3496,164 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>{campaignname}</t>
-        </is>
-      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Pashion.dk ApS</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="17" t="n">
         <v>120</v>
       </c>
-      <c r="C19" s="18" t="n">
+      <c r="C19" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="17" t="n">
         <v>1.8</v>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>09/16/25 16:05</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>78437</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I19" s="19" t="inlineStr">
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="J19" s="17" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
         </is>
       </c>
-      <c r="K19" s="17" t="inlineStr">
+      <c r="K19" s="16" t="inlineStr">
         <is>
           <t>41 EU - 8.5 US</t>
         </is>
       </c>
-      <c r="L19" s="17" t="inlineStr">
+      <c r="L19" s="16" t="inlineStr">
         <is>
           <t>310864-01</t>
         </is>
       </c>
-      <c r="M19" s="17" t="inlineStr">
+      <c r="M19" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N19" s="17" t="inlineStr">
+      <c r="N19" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O19" s="17" t="inlineStr">
+      <c r="O19" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P19" s="17" t="inlineStr"/>
-      <c r="Q19" s="17" t="inlineStr"/>
-      <c r="R19" s="17" t="inlineStr"/>
-      <c r="S19" s="17" t="inlineStr"/>
-      <c r="T19" s="17" t="inlineStr">
+      <c r="P19" s="16" t="inlineStr"/>
+      <c r="Q19" s="16" t="inlineStr"/>
+      <c r="R19" s="16" t="inlineStr"/>
+      <c r="S19" s="16" t="inlineStr"/>
+      <c r="T19" s="16" t="inlineStr">
         <is>
           <t>alfredirriak24@gmail.com</t>
         </is>
       </c>
-      <c r="U19" s="17" t="inlineStr">
+      <c r="U19" s="16" t="inlineStr">
         <is>
           <t>Alfredo Dueñas</t>
         </is>
       </c>
-      <c r="V19" s="17" t="inlineStr">
+      <c r="V19" s="16" t="inlineStr">
         <is>
           <t>Fernández</t>
         </is>
       </c>
-      <c r="W19" s="17" t="inlineStr">
+      <c r="W19" s="16" t="inlineStr">
         <is>
           <t>+34613250693</t>
         </is>
       </c>
-      <c r="X19" s="17" t="inlineStr">
+      <c r="X19" s="16" t="inlineStr">
         <is>
           <t>Repeat Customer (Order #2)</t>
         </is>
       </c>
-      <c r="Y19" s="17" t="inlineStr">
+      <c r="Y19" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z19" s="17" t="inlineStr">
+      <c r="Z19" s="16" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="AA19" s="17" t="inlineStr">
+      <c r="AA19" s="16" t="inlineStr">
         <is>
           <t>google</t>
         </is>
       </c>
-      <c r="AB19" s="17" t="inlineStr">
+      <c r="AB19" s="16" t="inlineStr">
         <is>
           <t>cpc</t>
         </is>
       </c>
-      <c r="AC19" s="17" t="inlineStr">
+      <c r="AC19" s="16" t="inlineStr">
         <is>
           <t>20498453736</t>
         </is>
       </c>
-      <c r="AD19" s="17" t="inlineStr"/>
-      <c r="AE19" s="17" t="inlineStr"/>
-      <c r="AF19" s="17" t="inlineStr"/>
+      <c r="AD19" s="16" t="inlineStr"/>
+      <c r="AE19" s="16" t="inlineStr"/>
+      <c r="AF19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LINKGAINS PTE.LTD.</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="n">
-        <v>165</v>
-      </c>
-      <c r="C20" s="20" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="D20" s="20" t="n">
-        <v>2.97</v>
+          <t>BlueVision Interactive Limited</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>88</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>1.58</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>09/16/25 15:09</t>
+          <t>09/15/25 11:50</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>78430</t>
+          <t>78383</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3666,24 +3666,24 @@
           <t>Retail</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Essentials Hoodie Dark Oatmeal, Essentials Hoodie Dark Oatmeal</t>
+          <t>Puma Speedcat OG Haute Coffee Frosted Ivory</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>M, S</t>
+          <t>37 EU - 5 US</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>192BT212113F, 192BT212113F</t>
+          <t>398846-31</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3707,33 +3707,33 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
-          <t>genezx99@gmail.com</t>
+          <t>ilargi-betea22@hotmail.com</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Zhao</t>
+          <t>Elisabet</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Xuan</t>
+          <t>Menen</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #2)</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr"/>
@@ -3744,140 +3744,148 @@
       <c r="AF20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>BlueVision Interactive Limited</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="C21" s="18" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>09/15/25 11:50</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>78383</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Pashion.dk ApS</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>09/15/25 11:46</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>78382</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>Puma Speedcat OG Haute Coffee Frosted Ivory</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>37 EU - 5 US</t>
-        </is>
-      </c>
-      <c r="L21" s="17" t="inlineStr">
-        <is>
-          <t>398846-31</t>
-        </is>
-      </c>
-      <c r="M21" s="17" t="inlineStr">
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>Puma Speedcat TTF Dark Chocolate Frosted Ivory</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>41 EU - 8 US</t>
+        </is>
+      </c>
+      <c r="L21" s="16" t="inlineStr">
+        <is>
+          <t>403903-01</t>
+        </is>
+      </c>
+      <c r="M21" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N21" s="17" t="inlineStr">
+      <c r="N21" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O21" s="17" t="inlineStr">
+      <c r="O21" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P21" s="17" t="inlineStr"/>
-      <c r="Q21" s="17" t="inlineStr"/>
-      <c r="R21" s="17" t="inlineStr"/>
-      <c r="S21" s="17" t="inlineStr"/>
-      <c r="T21" s="17" t="inlineStr">
-        <is>
-          <t>ilargi-betea22@hotmail.com</t>
-        </is>
-      </c>
-      <c r="U21" s="17" t="inlineStr">
-        <is>
-          <t>Elisabet</t>
-        </is>
-      </c>
-      <c r="V21" s="17" t="inlineStr">
-        <is>
-          <t>Menen</t>
-        </is>
-      </c>
-      <c r="W21" s="17" t="inlineStr"/>
-      <c r="X21" s="17" t="inlineStr">
+      <c r="P21" s="16" t="inlineStr"/>
+      <c r="Q21" s="16" t="inlineStr"/>
+      <c r="R21" s="16" t="inlineStr"/>
+      <c r="S21" s="16" t="inlineStr"/>
+      <c r="T21" s="16" t="inlineStr">
+        <is>
+          <t>luiscompostizo@gmail.com</t>
+        </is>
+      </c>
+      <c r="U21" s="16" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="V21" s="16" t="inlineStr">
+        <is>
+          <t>Compostizo Garcia</t>
+        </is>
+      </c>
+      <c r="W21" s="16" t="inlineStr">
+        <is>
+          <t>+34722237884</t>
+        </is>
+      </c>
+      <c r="X21" s="16" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y21" s="17" t="inlineStr">
+      <c r="Y21" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z21" s="17" t="inlineStr">
+      <c r="Z21" s="16" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="AA21" s="17" t="inlineStr"/>
-      <c r="AB21" s="17" t="inlineStr"/>
-      <c r="AC21" s="17" t="inlineStr"/>
-      <c r="AD21" s="17" t="inlineStr"/>
-      <c r="AE21" s="17" t="inlineStr"/>
-      <c r="AF21" s="17" t="inlineStr"/>
+      <c r="AA21" s="16" t="inlineStr">
+        <is>
+          <t>webgains</t>
+        </is>
+      </c>
+      <c r="AB21" s="16" t="inlineStr"/>
+      <c r="AC21" s="16" t="inlineStr"/>
+      <c r="AD21" s="16" t="inlineStr"/>
+      <c r="AE21" s="16" t="inlineStr"/>
+      <c r="AF21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="C22" s="20" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="D22" s="20" t="n">
-        <v>1.49</v>
+          <t>BlueVision Interactive Limited</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>96</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>1.73</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>09/14/25 12:50</t>
+          <t>09/14/25 22:07</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6891134681429</t>
+          <t>78374</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3890,24 +3898,24 @@
           <t>Retail</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I22" s="15" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Adidas Handball Spezial Core Black Pink</t>
+          <t>Adidas Samba OG Core Black</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>43.3 EU - 9.5 US</t>
+          <t>42.6 EU - 9 US</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>IE5897</t>
+          <t>B75807</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3931,17 +3939,17 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Slwoffi@hotmail.com</t>
+          <t>ydorgambide@gmail.com</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Yago</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Lwoff Ivanissevich</t>
+          <t>Dorgambide Dios</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
@@ -3955,7 +3963,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
@@ -3964,140 +3976,140 @@
       <c r="AF22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>BlueVision Interactive Limited</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>09/14/25 22:07</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>78374</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>LINKGAINS PTE.LTD.</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>165</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>09/16/25 15:09</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>78430</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I23" s="19" t="inlineStr">
+      <c r="I23" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="J23" s="17" t="inlineStr">
-        <is>
-          <t>Adidas Samba OG Core Black</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>42.6 EU - 9 US</t>
-        </is>
-      </c>
-      <c r="L23" s="17" t="inlineStr">
-        <is>
-          <t>B75807</t>
-        </is>
-      </c>
-      <c r="M23" s="17" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>Essentials Hoodie Dark Oatmeal, Essentials Hoodie Dark Oatmeal</t>
+        </is>
+      </c>
+      <c r="K23" s="16" t="inlineStr">
+        <is>
+          <t>M, S</t>
+        </is>
+      </c>
+      <c r="L23" s="16" t="inlineStr">
+        <is>
+          <t>192BT212113F, 192BT212113F</t>
+        </is>
+      </c>
+      <c r="M23" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N23" s="17" t="inlineStr">
+      <c r="N23" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O23" s="17" t="inlineStr">
+      <c r="O23" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P23" s="17" t="inlineStr"/>
-      <c r="Q23" s="17" t="inlineStr"/>
-      <c r="R23" s="17" t="inlineStr"/>
-      <c r="S23" s="17" t="inlineStr"/>
-      <c r="T23" s="17" t="inlineStr">
-        <is>
-          <t>ydorgambide@gmail.com</t>
-        </is>
-      </c>
-      <c r="U23" s="17" t="inlineStr">
-        <is>
-          <t>Yago</t>
-        </is>
-      </c>
-      <c r="V23" s="17" t="inlineStr">
-        <is>
-          <t>Dorgambide Dios</t>
-        </is>
-      </c>
-      <c r="W23" s="17" t="inlineStr"/>
-      <c r="X23" s="17" t="inlineStr">
+      <c r="P23" s="16" t="inlineStr"/>
+      <c r="Q23" s="16" t="inlineStr"/>
+      <c r="R23" s="16" t="inlineStr"/>
+      <c r="S23" s="16" t="inlineStr"/>
+      <c r="T23" s="16" t="inlineStr">
+        <is>
+          <t>genezx99@gmail.com</t>
+        </is>
+      </c>
+      <c r="U23" s="16" t="inlineStr">
+        <is>
+          <t>Zhao</t>
+        </is>
+      </c>
+      <c r="V23" s="16" t="inlineStr">
+        <is>
+          <t>Xuan</t>
+        </is>
+      </c>
+      <c r="W23" s="16" t="inlineStr"/>
+      <c r="X23" s="16" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y23" s="17" t="inlineStr">
+      <c r="Y23" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z23" s="17" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="AA23" s="17" t="inlineStr"/>
-      <c r="AB23" s="17" t="inlineStr"/>
-      <c r="AC23" s="17" t="inlineStr"/>
-      <c r="AD23" s="17" t="inlineStr"/>
-      <c r="AE23" s="17" t="inlineStr"/>
-      <c r="AF23" s="17" t="inlineStr"/>
+      <c r="Z23" s="16" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="AA23" s="16" t="inlineStr"/>
+      <c r="AB23" s="16" t="inlineStr"/>
+      <c r="AC23" s="16" t="inlineStr"/>
+      <c r="AD23" s="16" t="inlineStr"/>
+      <c r="AE23" s="16" t="inlineStr"/>
+      <c r="AF23" s="16" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pashion.dk ApS</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="n">
-        <v>120</v>
-      </c>
-      <c r="C24" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="D24" s="20" t="n">
-        <v>1.8</v>
+          <t>Purplee Corp</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>1.49</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>09/15/25 11:46</t>
+          <t>09/14/25 12:50</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>78382</t>
+          <t>6891134681429</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4107,27 +4119,27 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>5%</t>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>6%</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Puma Speedcat TTF Dark Chocolate Frosted Ivory</t>
+          <t>Adidas Handball Spezial Core Black Pink</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>41 EU - 8 US</t>
+          <t>43.3 EU - 9.5 US</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>403903-01</t>
+          <t>IE5897</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -4151,24 +4163,20 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
-          <t>luiscompostizo@gmail.com</t>
+          <t>Slwoffi@hotmail.com</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Compostizo Garcia</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>+34722237884</t>
-        </is>
-      </c>
+          <t>Lwoff Ivanissevich</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
           <t>First Order</t>
@@ -4179,16 +4187,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>webgains</t>
-        </is>
-      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
@@ -4196,140 +4196,144 @@
       <c r="AF24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>BlueVision Interactive Limited</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="n">
-        <v>750</v>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>09/13/25 10:43</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>78157</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Digital Expand</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>550</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>09/11/25 16:14</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>6887025475925</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="H25" s="16" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I25" s="19" t="inlineStr">
+      <c r="I25" s="18" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>Dunk Low Off-White Lot 21</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>44 EU - 10 US</t>
-        </is>
-      </c>
-      <c r="L25" s="17" t="inlineStr">
-        <is>
-          <t>DM1602-100</t>
-        </is>
-      </c>
-      <c r="M25" s="17" t="inlineStr">
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>Air Jordan 1 Retro Low OG SP Travis Scott Velvet Brown</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
+          <t>42 EU - 8.5 US</t>
+        </is>
+      </c>
+      <c r="L25" s="16" t="inlineStr">
+        <is>
+          <t>DM7866-202</t>
+        </is>
+      </c>
+      <c r="M25" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N25" s="17" t="inlineStr">
+      <c r="N25" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O25" s="17" t="inlineStr">
+      <c r="O25" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P25" s="17" t="inlineStr"/>
-      <c r="Q25" s="17" t="inlineStr"/>
-      <c r="R25" s="17" t="inlineStr"/>
-      <c r="S25" s="17" t="inlineStr"/>
-      <c r="T25" s="17" t="inlineStr">
-        <is>
-          <t>juudith.rg@gmail.com</t>
-        </is>
-      </c>
-      <c r="U25" s="17" t="inlineStr">
-        <is>
-          <t>Judith</t>
-        </is>
-      </c>
-      <c r="V25" s="17" t="inlineStr">
-        <is>
-          <t>Robles Garcia</t>
-        </is>
-      </c>
-      <c r="W25" s="17" t="inlineStr"/>
-      <c r="X25" s="17" t="inlineStr">
-        <is>
-          <t>First Order</t>
-        </is>
-      </c>
-      <c r="Y25" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z25" s="17" t="inlineStr">
+      <c r="P25" s="16" t="inlineStr"/>
+      <c r="Q25" s="16" t="inlineStr"/>
+      <c r="R25" s="16" t="inlineStr"/>
+      <c r="S25" s="16" t="inlineStr"/>
+      <c r="T25" s="16" t="inlineStr">
+        <is>
+          <t>cristiancampos26500@gmail.com</t>
+        </is>
+      </c>
+      <c r="U25" s="16" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="V25" s="16" t="inlineStr">
+        <is>
+          <t>Campos Mata</t>
+        </is>
+      </c>
+      <c r="W25" s="16" t="inlineStr">
+        <is>
+          <t>+34632623867</t>
+        </is>
+      </c>
+      <c r="X25" s="16" t="inlineStr">
+        <is>
+          <t>Repeat Customer (Order #3)</t>
+        </is>
+      </c>
+      <c r="Y25" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z25" s="16" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="AA25" s="17" t="inlineStr"/>
-      <c r="AB25" s="17" t="inlineStr"/>
-      <c r="AC25" s="17" t="inlineStr"/>
-      <c r="AD25" s="17" t="inlineStr"/>
-      <c r="AE25" s="17" t="inlineStr"/>
-      <c r="AF25" s="17" t="inlineStr"/>
+      <c r="AA25" s="16" t="inlineStr"/>
+      <c r="AB25" s="16" t="inlineStr"/>
+      <c r="AC25" s="16" t="inlineStr"/>
+      <c r="AD25" s="16" t="inlineStr"/>
+      <c r="AE25" s="16" t="inlineStr"/>
+      <c r="AF25" s="16" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="n">
-        <v>550</v>
-      </c>
-      <c r="C26" s="20" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="D26" s="20" t="n">
-        <v>8.25</v>
+          <t>BlueVision Interactive Limited</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>750</v>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>11.25</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>09/11/25 16:14</t>
+          <t>09/13/25 10:43</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6887025475925</t>
+          <t>78157</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4342,24 +4346,24 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="I26" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Retro Low OG SP Travis Scott Velvet Brown</t>
+          <t>Dunk Low Off-White Lot 21</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>42 EU - 8.5 US</t>
+          <t>44 EU - 10 US</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>DM7866-202</t>
+          <t>DM1602-100</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -4383,32 +4387,28 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
-          <t>cristiancampos26500@gmail.com</t>
+          <t>juudith.rg@gmail.com</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Cristian</t>
+          <t>Judith</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Campos Mata</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>+34632623867</t>
-        </is>
-      </c>
+          <t>Robles Garcia</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Repeat Customer (Order #3)</t>
+          <t>First Order</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -4424,405 +4424,405 @@
       <c r="AF26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Shoparize</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="17" t="n">
         <v>85</v>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C27" s="17" t="n">
         <v>5.1</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="17" t="n">
         <v>1.53</v>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>09/10/25 16:40</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>77926</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G27" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I27" s="19" t="inlineStr">
+      <c r="I27" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="J27" s="17" t="inlineStr">
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>Adidas SL 72 OG Maroon Preloved Brown</t>
         </is>
       </c>
-      <c r="K27" s="17" t="inlineStr">
+      <c r="K27" s="16" t="inlineStr">
         <is>
           <t>39.3 EU - 6.5 US</t>
         </is>
       </c>
-      <c r="L27" s="17" t="inlineStr">
+      <c r="L27" s="16" t="inlineStr">
         <is>
           <t>IE3425</t>
         </is>
       </c>
-      <c r="M27" s="17" t="inlineStr">
+      <c r="M27" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N27" s="17" t="inlineStr">
+      <c r="N27" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O27" s="17" t="inlineStr">
+      <c r="O27" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P27" s="17" t="inlineStr"/>
-      <c r="Q27" s="17" t="inlineStr"/>
-      <c r="R27" s="17" t="inlineStr"/>
-      <c r="S27" s="17" t="inlineStr"/>
-      <c r="T27" s="17" t="inlineStr">
+      <c r="P27" s="16" t="inlineStr"/>
+      <c r="Q27" s="16" t="inlineStr"/>
+      <c r="R27" s="16" t="inlineStr"/>
+      <c r="S27" s="16" t="inlineStr"/>
+      <c r="T27" s="16" t="inlineStr">
         <is>
           <t>paula.ar14@gmail.com</t>
         </is>
       </c>
-      <c r="U27" s="17" t="inlineStr">
+      <c r="U27" s="16" t="inlineStr">
         <is>
           <t>Paula</t>
         </is>
       </c>
-      <c r="V27" s="17" t="inlineStr">
+      <c r="V27" s="16" t="inlineStr">
         <is>
           <t>Armero Ramón</t>
         </is>
       </c>
-      <c r="W27" s="17" t="inlineStr"/>
-      <c r="X27" s="17" t="inlineStr">
+      <c r="W27" s="16" t="inlineStr"/>
+      <c r="X27" s="16" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y27" s="17" t="inlineStr">
+      <c r="Y27" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z27" s="17" t="inlineStr">
+      <c r="Z27" s="16" t="inlineStr">
         <is>
           <t>https://www.shoparize.com/</t>
         </is>
       </c>
-      <c r="AA27" s="17" t="inlineStr">
+      <c r="AA27" s="16" t="inlineStr">
         <is>
           <t>webgains</t>
         </is>
       </c>
-      <c r="AB27" s="17" t="inlineStr"/>
-      <c r="AC27" s="17" t="inlineStr"/>
-      <c r="AD27" s="17" t="inlineStr"/>
-      <c r="AE27" s="17" t="inlineStr"/>
-      <c r="AF27" s="17" t="inlineStr"/>
+      <c r="AB27" s="16" t="inlineStr"/>
+      <c r="AC27" s="16" t="inlineStr"/>
+      <c r="AD27" s="16" t="inlineStr"/>
+      <c r="AE27" s="16" t="inlineStr"/>
+      <c r="AF27" s="16" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Klarna Bank AB UK Branch</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>153</v>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>09/10/25 09:03</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>77873</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Air Force 1 Rope Laces</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>38 EU - 5.5 US</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>CW2288-111ME</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>kaaa-95@hotmail.com</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Serrano Sánchez</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>First Order</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>an unknown source</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>webgains</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>SID Middle East LLC</t>
         </is>
       </c>
-      <c r="B28" s="23" t="n">
+      <c r="B29" s="23" t="n">
         <v>120.42</v>
       </c>
-      <c r="C28" s="23" t="n">
+      <c r="C29" s="23" t="n">
         <v>7.23</v>
       </c>
-      <c r="D28" s="23" t="n">
+      <c r="D29" s="23" t="n">
         <v>2.17</v>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>09/10/25 11:03</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>77880</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I28" s="24" t="inlineStr">
+      <c r="I29" s="24" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="J28" s="22" t="inlineStr">
+      <c r="J29" s="22" t="inlineStr">
         <is>
           <t>Puma LaMelo Ball LaFrancé 3x Black</t>
         </is>
       </c>
-      <c r="K28" s="22" t="inlineStr">
+      <c r="K29" s="22" t="inlineStr">
         <is>
           <t>42 EU - 9 US</t>
         </is>
       </c>
-      <c r="L28" s="22" t="inlineStr">
+      <c r="L29" s="22" t="inlineStr">
         <is>
           <t>313081-01</t>
         </is>
       </c>
-      <c r="M28" s="22" t="inlineStr">
+      <c r="M29" s="22" t="inlineStr">
         <is>
           <t>PARTIALLY_REFUNDED</t>
         </is>
       </c>
-      <c r="N28" s="22" t="inlineStr">
+      <c r="N29" s="22" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O28" s="22" t="inlineStr">
+      <c r="O29" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P28" s="22" t="inlineStr">
+      <c r="P29" s="22" t="inlineStr">
         <is>
           <t>PARTIALLY_REFUNDED</t>
         </is>
       </c>
-      <c r="Q28" s="22" t="inlineStr">
+      <c r="Q29" s="22" t="inlineStr">
         <is>
           <t>7.89 EUR / 120.42 EUR</t>
         </is>
       </c>
-      <c r="R28" s="22" t="inlineStr"/>
-      <c r="S28" s="22" t="inlineStr">
+      <c r="R29" s="22" t="inlineStr"/>
+      <c r="S29" s="22" t="inlineStr">
         <is>
           <t>Issue (PARTIALLY REFUNDED)</t>
         </is>
       </c>
-      <c r="T28" s="22" t="inlineStr">
+      <c r="T29" s="22" t="inlineStr">
         <is>
           <t>damasaru.nicu@gmail.com</t>
         </is>
       </c>
-      <c r="U28" s="22" t="inlineStr">
+      <c r="U29" s="22" t="inlineStr">
         <is>
           <t>damasaru</t>
         </is>
       </c>
-      <c r="V28" s="22" t="inlineStr">
+      <c r="V29" s="22" t="inlineStr">
         <is>
           <t>nicu</t>
         </is>
       </c>
-      <c r="W28" s="22" t="inlineStr"/>
-      <c r="X28" s="22" t="inlineStr">
+      <c r="W29" s="22" t="inlineStr"/>
+      <c r="X29" s="22" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y28" s="22" t="inlineStr">
+      <c r="Y29" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z28" s="22" t="inlineStr">
+      <c r="Z29" s="22" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="AA28" s="22" t="inlineStr">
+      <c r="AA29" s="22" t="inlineStr">
         <is>
           <t>google</t>
         </is>
       </c>
-      <c r="AB28" s="22" t="inlineStr">
+      <c r="AB29" s="22" t="inlineStr">
         <is>
           <t>product_sync</t>
         </is>
       </c>
-      <c r="AC28" s="22" t="inlineStr">
+      <c r="AC29" s="22" t="inlineStr">
         <is>
           <t>sag_organic</t>
         </is>
       </c>
-      <c r="AD28" s="22" t="inlineStr"/>
-      <c r="AE28" s="22" t="inlineStr">
+      <c r="AD29" s="22" t="inlineStr"/>
+      <c r="AE29" s="22" t="inlineStr">
         <is>
           <t>sag_organic</t>
         </is>
       </c>
-      <c r="AF28" s="22" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Klarna Bank AB UK Branch</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="n">
-        <v>153</v>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>09/10/25 09:03</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>77873</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I29" s="19" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>Air Force 1 Rope Laces</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="inlineStr">
-        <is>
-          <t>38 EU - 5.5 US</t>
-        </is>
-      </c>
-      <c r="L29" s="17" t="inlineStr">
-        <is>
-          <t>CW2288-111ME</t>
-        </is>
-      </c>
-      <c r="M29" s="17" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
-      </c>
-      <c r="N29" s="17" t="inlineStr">
-        <is>
-          <t>FULFILLED</t>
-        </is>
-      </c>
-      <c r="O29" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P29" s="17" t="inlineStr"/>
-      <c r="Q29" s="17" t="inlineStr"/>
-      <c r="R29" s="17" t="inlineStr"/>
-      <c r="S29" s="17" t="inlineStr"/>
-      <c r="T29" s="17" t="inlineStr">
-        <is>
-          <t>kaaa-95@hotmail.com</t>
-        </is>
-      </c>
-      <c r="U29" s="17" t="inlineStr">
-        <is>
-          <t>Karen</t>
-        </is>
-      </c>
-      <c r="V29" s="17" t="inlineStr">
-        <is>
-          <t>Serrano Sánchez</t>
-        </is>
-      </c>
-      <c r="W29" s="17" t="inlineStr"/>
-      <c r="X29" s="17" t="inlineStr">
-        <is>
-          <t>First Order</t>
-        </is>
-      </c>
-      <c r="Y29" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z29" s="17" t="inlineStr">
-        <is>
-          <t>an unknown source</t>
-        </is>
-      </c>
-      <c r="AA29" s="17" t="inlineStr">
-        <is>
-          <t>webgains</t>
-        </is>
-      </c>
-      <c r="AB29" s="17" t="inlineStr"/>
-      <c r="AC29" s="17" t="inlineStr"/>
-      <c r="AD29" s="17" t="inlineStr"/>
-      <c r="AE29" s="17" t="inlineStr"/>
-      <c r="AF29" s="17" t="inlineStr"/>
+      <c r="AF29" s="22" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LINKGAINS PTE.LTD.</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="n">
-        <v>335</v>
-      </c>
-      <c r="C30" s="20" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="D30" s="20" t="n">
-        <v>5.03</v>
+          <t>Skimbit LTD</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>1.38</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>09/09/25 17:32</t>
+          <t>09/09/25 21:51</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>77821</t>
+          <t>77865</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4830,24 +4830,24 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I30" s="21" t="inlineStr">
+      <c r="I30" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>ASICS Gel-NYC Cream Arctic Sky</t>
+          <t>Crep Protect Crep Pill, Adidas Samba OG Earth Strata Wonder White</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>40 EU - 7 US</t>
+          <t>, 39.3 EU - 6.5 US</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1203A383-107</t>
+          <t>crap 22, JI3184</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -4871,17 +4871,17 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>gestoriapradillo@gmail.com</t>
+          <t>moghaddasi.majid@gmail.com</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>LAURA</t>
+          <t>Majid</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>BORRAJO ROMERO</t>
+          <t>Moghaddasi</t>
         </is>
       </c>
       <c r="W30" t="inlineStr"/>
@@ -4912,140 +4912,140 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
+          <t>22980696441</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>Adidas Samba OG Earth Strata Wonder White</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>LINKGAINS PTE.LTD.</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n">
+        <v>335</v>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>09/09/25 17:32</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>77821</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I31" s="18" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>ASICS Gel-NYC Cream Arctic Sky</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>40 EU - 7 US</t>
+        </is>
+      </c>
+      <c r="L31" s="16" t="inlineStr">
+        <is>
+          <t>1203A383-107</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O31" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P31" s="16" t="inlineStr"/>
+      <c r="Q31" s="16" t="inlineStr"/>
+      <c r="R31" s="16" t="inlineStr"/>
+      <c r="S31" s="16" t="inlineStr"/>
+      <c r="T31" s="16" t="inlineStr">
+        <is>
+          <t>gestoriapradillo@gmail.com</t>
+        </is>
+      </c>
+      <c r="U31" s="16" t="inlineStr">
+        <is>
+          <t>LAURA</t>
+        </is>
+      </c>
+      <c r="V31" s="16" t="inlineStr">
+        <is>
+          <t>BORRAJO ROMERO</t>
+        </is>
+      </c>
+      <c r="W31" s="16" t="inlineStr"/>
+      <c r="X31" s="16" t="inlineStr">
+        <is>
+          <t>First Order</t>
+        </is>
+      </c>
+      <c r="Y31" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z31" s="16" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="AA31" s="16" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="AB31" s="16" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="AC31" s="16" t="inlineStr">
+        <is>
           <t>21366334315</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Skimbit LTD</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>09/09/25 21:51</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>77865</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>Crep Protect Crep Pill, Adidas Samba OG Earth Strata Wonder White</t>
-        </is>
-      </c>
-      <c r="K31" s="17" t="inlineStr">
-        <is>
-          <t>, 39.3 EU - 6.5 US</t>
-        </is>
-      </c>
-      <c r="L31" s="17" t="inlineStr">
-        <is>
-          <t>crap 22, JI3184</t>
-        </is>
-      </c>
-      <c r="M31" s="17" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
-      </c>
-      <c r="N31" s="17" t="inlineStr">
-        <is>
-          <t>FULFILLED</t>
-        </is>
-      </c>
-      <c r="O31" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P31" s="17" t="inlineStr"/>
-      <c r="Q31" s="17" t="inlineStr"/>
-      <c r="R31" s="17" t="inlineStr"/>
-      <c r="S31" s="17" t="inlineStr"/>
-      <c r="T31" s="17" t="inlineStr">
-        <is>
-          <t>moghaddasi.majid@gmail.com</t>
-        </is>
-      </c>
-      <c r="U31" s="17" t="inlineStr">
-        <is>
-          <t>Majid</t>
-        </is>
-      </c>
-      <c r="V31" s="17" t="inlineStr">
-        <is>
-          <t>Moghaddasi</t>
-        </is>
-      </c>
-      <c r="W31" s="17" t="inlineStr"/>
-      <c r="X31" s="17" t="inlineStr">
-        <is>
-          <t>First Order</t>
-        </is>
-      </c>
-      <c r="Y31" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z31" s="17" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="AA31" s="17" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="AB31" s="17" t="inlineStr">
-        <is>
-          <t>cpc</t>
-        </is>
-      </c>
-      <c r="AC31" s="17" t="inlineStr">
-        <is>
-          <t>22980696441</t>
-        </is>
-      </c>
-      <c r="AD31" s="17" t="inlineStr"/>
-      <c r="AE31" s="17" t="inlineStr">
-        <is>
-          <t>Adidas Samba OG Earth Strata Wonder White</t>
-        </is>
-      </c>
-      <c r="AF31" s="17" t="inlineStr"/>
+      <c r="AD31" s="16" t="inlineStr"/>
+      <c r="AE31" s="16" t="inlineStr"/>
+      <c r="AF31" s="16" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5053,13 +5053,13 @@
           <t>Webravo SRL</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n">
+      <c r="B32" s="14" t="n">
         <v>85</v>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C32" s="14" t="n">
         <v>5.1</v>
       </c>
-      <c r="D32" s="20" t="n">
+      <c r="D32" s="14" t="n">
         <v>1.53</v>
       </c>
       <c r="E32" t="inlineStr">
@@ -5082,7 +5082,7 @@
           <t>Retail</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
+      <c r="I32" s="15" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -5160,144 +5160,144 @@
       <c r="AF32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Skimbit LTD</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="17" t="n">
         <v>88</v>
       </c>
-      <c r="C33" s="18" t="n">
+      <c r="C33" s="17" t="n">
         <v>5.28</v>
       </c>
-      <c r="D33" s="18" t="n">
+      <c r="D33" s="17" t="n">
         <v>1.58</v>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>09/08/25 11:06</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>77687</t>
         </is>
       </c>
-      <c r="G33" s="17" t="inlineStr">
+      <c r="G33" s="16" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="H33" s="17" t="inlineStr">
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I33" s="19" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="J33" s="17" t="inlineStr">
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>Adidas Handball Spezial Night Indigo Chalk White</t>
         </is>
       </c>
-      <c r="K33" s="17" t="inlineStr">
+      <c r="K33" s="16" t="inlineStr">
         <is>
           <t>38.6 EU - 6 US</t>
         </is>
       </c>
-      <c r="L33" s="17" t="inlineStr">
+      <c r="L33" s="16" t="inlineStr">
         <is>
           <t>JH5440</t>
         </is>
       </c>
-      <c r="M33" s="17" t="inlineStr">
+      <c r="M33" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N33" s="17" t="inlineStr">
+      <c r="N33" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O33" s="17" t="inlineStr">
+      <c r="O33" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P33" s="17" t="inlineStr"/>
-      <c r="Q33" s="17" t="inlineStr"/>
-      <c r="R33" s="17" t="inlineStr"/>
-      <c r="S33" s="17" t="inlineStr"/>
-      <c r="T33" s="17" t="inlineStr">
+      <c r="P33" s="16" t="inlineStr"/>
+      <c r="Q33" s="16" t="inlineStr"/>
+      <c r="R33" s="16" t="inlineStr"/>
+      <c r="S33" s="16" t="inlineStr"/>
+      <c r="T33" s="16" t="inlineStr">
         <is>
           <t>jeff2034@gmail.com</t>
         </is>
       </c>
-      <c r="U33" s="17" t="inlineStr">
+      <c r="U33" s="16" t="inlineStr">
         <is>
           <t>Jean-françois</t>
         </is>
       </c>
-      <c r="V33" s="17" t="inlineStr">
+      <c r="V33" s="16" t="inlineStr">
         <is>
           <t>Joly</t>
         </is>
       </c>
-      <c r="W33" s="17" t="inlineStr">
+      <c r="W33" s="16" t="inlineStr">
         <is>
           <t>+33664376736</t>
         </is>
       </c>
-      <c r="X33" s="17" t="inlineStr">
+      <c r="X33" s="16" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y33" s="17" t="inlineStr">
+      <c r="Y33" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z33" s="17" t="inlineStr">
+      <c r="Z33" s="16" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="AA33" s="17" t="inlineStr"/>
-      <c r="AB33" s="17" t="inlineStr"/>
-      <c r="AC33" s="17" t="inlineStr"/>
-      <c r="AD33" s="17" t="inlineStr"/>
-      <c r="AE33" s="17" t="inlineStr"/>
-      <c r="AF33" s="17" t="inlineStr"/>
+      <c r="AA33" s="16" t="inlineStr"/>
+      <c r="AB33" s="16" t="inlineStr"/>
+      <c r="AC33" s="16" t="inlineStr"/>
+      <c r="AD33" s="16" t="inlineStr"/>
+      <c r="AE33" s="16" t="inlineStr"/>
+      <c r="AF33" s="16" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LINKPREFER LIMITED</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="n">
-        <v>280</v>
-      </c>
-      <c r="C34" s="20" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="D34" s="20" t="n">
-        <v>5.04</v>
+          <t>Shoparize</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>1.26</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>09/07/25 15:13</t>
+          <t>09/09/25 01:55</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>77607</t>
+          <t>77760</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5310,24 +5310,24 @@
           <t>Retail</t>
         </is>
       </c>
-      <c r="I34" s="21" t="inlineStr">
+      <c r="I34" s="15" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Adidas Gazelle Indoor Bad Bunny Cabo Rojo</t>
+          <t>Adidas SL 72 RS Black Carbon</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>38.6 EU - 6 US</t>
+          <t>44 EU - 10 US</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>JS5052</t>
+          <t>JH5098</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -5351,22 +5351,22 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
-          <t>browses.owners-8u@icloud.com</t>
+          <t>manuelopez.mlg@gmail.com</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Schweitzer</t>
+          <t>López Garrido</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>+34680952342</t>
+          <t>+34673369013</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -5386,170 +5386,154 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>CAMPAÑA_ESCALADO_AD</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>120206246202400135</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>120231190735490135</t>
-        </is>
-      </c>
+          <t>webgains</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>LINKGAINS PTE.LTD.</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>09/07/25 15:51</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>77615</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Fullstaak SA</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="C35" s="17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>09/06/25 16:11</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>6879153488213</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H35" s="17" t="inlineStr">
+      <c r="H35" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I35" s="19" t="inlineStr">
+      <c r="I35" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="J35" s="17" t="inlineStr">
-        <is>
-          <t>Puma Arizona Zebra</t>
-        </is>
-      </c>
-      <c r="K35" s="17" t="inlineStr">
-        <is>
-          <t>37 EU - 5 US</t>
-        </is>
-      </c>
-      <c r="L35" s="17" t="inlineStr">
-        <is>
-          <t>404398-01</t>
-        </is>
-      </c>
-      <c r="M35" s="17" t="inlineStr">
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>Puma H-Street OG Fizzy Green</t>
+        </is>
+      </c>
+      <c r="K35" s="16" t="inlineStr">
+        <is>
+          <t>45 EU - 11.5 US</t>
+        </is>
+      </c>
+      <c r="L35" s="16" t="inlineStr">
+        <is>
+          <t>403692-01</t>
+        </is>
+      </c>
+      <c r="M35" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N35" s="17" t="inlineStr">
+      <c r="N35" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O35" s="17" t="inlineStr">
+      <c r="O35" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P35" s="17" t="inlineStr"/>
-      <c r="Q35" s="17" t="inlineStr"/>
-      <c r="R35" s="17" t="inlineStr"/>
-      <c r="S35" s="17" t="inlineStr"/>
-      <c r="T35" s="17" t="inlineStr">
-        <is>
-          <t>jessijuan2014@gmail.com</t>
-        </is>
-      </c>
-      <c r="U35" s="17" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="V35" s="17" t="inlineStr">
-        <is>
-          <t>Llopis</t>
-        </is>
-      </c>
-      <c r="W35" s="17" t="inlineStr">
-        <is>
-          <t>+34650397617</t>
-        </is>
-      </c>
-      <c r="X35" s="17" t="inlineStr">
-        <is>
-          <t>Repeat Customer (Order #3)</t>
-        </is>
-      </c>
-      <c r="Y35" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z35" s="17" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="AA35" s="17" t="inlineStr"/>
-      <c r="AB35" s="17" t="inlineStr"/>
-      <c r="AC35" s="17" t="inlineStr"/>
-      <c r="AD35" s="17" t="inlineStr"/>
-      <c r="AE35" s="17" t="inlineStr"/>
-      <c r="AF35" s="17" t="inlineStr"/>
+      <c r="P35" s="16" t="inlineStr"/>
+      <c r="Q35" s="16" t="inlineStr"/>
+      <c r="R35" s="16" t="inlineStr"/>
+      <c r="S35" s="16" t="inlineStr"/>
+      <c r="T35" s="16" t="inlineStr">
+        <is>
+          <t>manuel@embutidosgarcializana.com</t>
+        </is>
+      </c>
+      <c r="U35" s="16" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="V35" s="16" t="inlineStr">
+        <is>
+          <t>Garcia morcillo</t>
+        </is>
+      </c>
+      <c r="W35" s="16" t="inlineStr">
+        <is>
+          <t>+34626229624</t>
+        </is>
+      </c>
+      <c r="X35" s="16" t="inlineStr">
+        <is>
+          <t>First Order</t>
+        </is>
+      </c>
+      <c r="Y35" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z35" s="16" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="AA35" s="16" t="inlineStr"/>
+      <c r="AB35" s="16" t="inlineStr"/>
+      <c r="AC35" s="16" t="inlineStr"/>
+      <c r="AD35" s="16" t="inlineStr"/>
+      <c r="AE35" s="16" t="inlineStr"/>
+      <c r="AF35" s="16" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="C36" s="20" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="D36" s="20" t="n">
-        <v>1.24</v>
+          <t>LINKPREFER LIMITED</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>280</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>5.04</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>09/07/25 14:43</t>
+          <t>09/07/25 15:13</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>77604</t>
+          <t>77607</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5559,27 +5543,27 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I36" s="21" t="inlineStr">
-        <is>
-          <t>5%</t>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>6%</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Adidas Handball Spezial Green White Gum</t>
+          <t>Adidas Gazelle Indoor Bad Bunny Cabo Rojo</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>37.3 EU - 5 US</t>
+          <t>38.6 EU - 6 US</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>JH5438</t>
+          <t>JS5052</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -5603,22 +5587,22 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
         <is>
-          <t>aichaamghar198@gmail.com</t>
+          <t>browses.owners-8u@icloud.com</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Aicha</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Amghar</t>
+          <t>Schweitzer</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>+34602370988</t>
+          <t>+34680952342</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -5633,159 +5617,175 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
+          <t>an unknown source</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>CAMPAÑA_ESCALADO_AD</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>120206246202400135</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>120231190735490135</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>LINKGAINS PTE.LTD.</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>09/07/25 15:51</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>77615</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>Puma Arizona Zebra</t>
+        </is>
+      </c>
+      <c r="K37" s="16" t="inlineStr">
+        <is>
+          <t>37 EU - 5 US</t>
+        </is>
+      </c>
+      <c r="L37" s="16" t="inlineStr">
+        <is>
+          <t>404398-01</t>
+        </is>
+      </c>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="N37" s="16" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O37" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P37" s="16" t="inlineStr"/>
+      <c r="Q37" s="16" t="inlineStr"/>
+      <c r="R37" s="16" t="inlineStr"/>
+      <c r="S37" s="16" t="inlineStr"/>
+      <c r="T37" s="16" t="inlineStr">
+        <is>
+          <t>jessijuan2014@gmail.com</t>
+        </is>
+      </c>
+      <c r="U37" s="16" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="V37" s="16" t="inlineStr">
+        <is>
+          <t>Llopis</t>
+        </is>
+      </c>
+      <c r="W37" s="16" t="inlineStr">
+        <is>
+          <t>+34650397617</t>
+        </is>
+      </c>
+      <c r="X37" s="16" t="inlineStr">
+        <is>
+          <t>Repeat Customer (Order #3)</t>
+        </is>
+      </c>
+      <c r="Y37" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z37" s="16" t="inlineStr">
+        <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>Shoparize</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="C37" s="18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>09/09/25 01:55</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>77760</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H37" s="17" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I37" s="19" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="J37" s="17" t="inlineStr">
-        <is>
-          <t>Adidas SL 72 RS Black Carbon</t>
-        </is>
-      </c>
-      <c r="K37" s="17" t="inlineStr">
-        <is>
-          <t>44 EU - 10 US</t>
-        </is>
-      </c>
-      <c r="L37" s="17" t="inlineStr">
-        <is>
-          <t>JH5098</t>
-        </is>
-      </c>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
-      </c>
-      <c r="N37" s="17" t="inlineStr">
-        <is>
-          <t>FULFILLED</t>
-        </is>
-      </c>
-      <c r="O37" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P37" s="17" t="inlineStr"/>
-      <c r="Q37" s="17" t="inlineStr"/>
-      <c r="R37" s="17" t="inlineStr"/>
-      <c r="S37" s="17" t="inlineStr"/>
-      <c r="T37" s="17" t="inlineStr">
-        <is>
-          <t>manuelopez.mlg@gmail.com</t>
-        </is>
-      </c>
-      <c r="U37" s="17" t="inlineStr">
-        <is>
-          <t>Manuel</t>
-        </is>
-      </c>
-      <c r="V37" s="17" t="inlineStr">
-        <is>
-          <t>López Garrido</t>
-        </is>
-      </c>
-      <c r="W37" s="17" t="inlineStr">
-        <is>
-          <t>+34673369013</t>
-        </is>
-      </c>
-      <c r="X37" s="17" t="inlineStr">
-        <is>
-          <t>First Order</t>
-        </is>
-      </c>
-      <c r="Y37" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z37" s="17" t="inlineStr">
-        <is>
-          <t>an unknown source</t>
-        </is>
-      </c>
-      <c r="AA37" s="17" t="inlineStr">
-        <is>
-          <t>webgains</t>
-        </is>
-      </c>
-      <c r="AB37" s="17" t="inlineStr"/>
-      <c r="AC37" s="17" t="inlineStr"/>
-      <c r="AD37" s="17" t="inlineStr"/>
-      <c r="AE37" s="17" t="inlineStr"/>
-      <c r="AF37" s="17" t="inlineStr"/>
+      <c r="AA37" s="16" t="inlineStr"/>
+      <c r="AB37" s="16" t="inlineStr"/>
+      <c r="AC37" s="16" t="inlineStr"/>
+      <c r="AD37" s="16" t="inlineStr"/>
+      <c r="AE37" s="16" t="inlineStr"/>
+      <c r="AF37" s="16" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fullstaak SA</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="C38" s="20" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="D38" s="20" t="n">
-        <v>1.22</v>
+          <t>BlueVision Interactive Limited</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>1.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>09/06/25 16:11</t>
+          <t>09/05/25 20:13</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>6879153488213</t>
+          <t>77431</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5795,27 +5795,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I38" s="21" t="inlineStr">
-        <is>
-          <t>6%</t>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>5%</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Puma H-Street OG Fizzy Green</t>
+          <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>45 EU - 11.5 US</t>
+          <t>43 EU - 10 US</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>403692-01</t>
+          <t>310864-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -5839,37 +5839,37 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
-          <t>manuel@embutidosgarcializana.com</t>
+          <t>pj_sanchez17@yahoo.es</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Garcia morcillo</t>
+          <t>Sanchez fernandez</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>+34626229624</t>
+          <t>+34655472907</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>First Order</t>
+          <t>Repeat Customer (Order #2)</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr"/>
@@ -5880,140 +5880,144 @@
       <c r="AF38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>Pashion.dk ApS</t>
-        </is>
-      </c>
-      <c r="B39" s="18" t="n">
-        <v>99</v>
-      </c>
-      <c r="C39" s="18" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>09/05/25 16:59</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>6877597237589</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Purplee Corp</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>09/07/25 14:43</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>77604</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H39" s="17" t="inlineStr">
+      <c r="H39" s="16" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I39" s="19" t="inlineStr">
+      <c r="I39" s="18" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="J39" s="17" t="inlineStr">
-        <is>
-          <t>Adidas Handball Spezial Earth Strata Gum</t>
-        </is>
-      </c>
-      <c r="K39" s="17" t="inlineStr">
-        <is>
-          <t>38 EU - 5.5 US</t>
-        </is>
-      </c>
-      <c r="L39" s="17" t="inlineStr">
-        <is>
-          <t>IF6490</t>
-        </is>
-      </c>
-      <c r="M39" s="17" t="inlineStr">
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>Adidas Handball Spezial Green White Gum</t>
+        </is>
+      </c>
+      <c r="K39" s="16" t="inlineStr">
+        <is>
+          <t>37.3 EU - 5 US</t>
+        </is>
+      </c>
+      <c r="L39" s="16" t="inlineStr">
+        <is>
+          <t>JH5438</t>
+        </is>
+      </c>
+      <c r="M39" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N39" s="17" t="inlineStr">
+      <c r="N39" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O39" s="17" t="inlineStr">
+      <c r="O39" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P39" s="17" t="inlineStr"/>
-      <c r="Q39" s="17" t="inlineStr"/>
-      <c r="R39" s="17" t="inlineStr"/>
-      <c r="S39" s="17" t="inlineStr"/>
-      <c r="T39" s="17" t="inlineStr">
-        <is>
-          <t>tatiana7201@gmail.com</t>
-        </is>
-      </c>
-      <c r="U39" s="17" t="inlineStr">
-        <is>
-          <t>Tatiana</t>
-        </is>
-      </c>
-      <c r="V39" s="17" t="inlineStr">
-        <is>
-          <t>Silva Aragonés</t>
-        </is>
-      </c>
-      <c r="W39" s="17" t="inlineStr">
-        <is>
-          <t>+34618535989</t>
-        </is>
-      </c>
-      <c r="X39" s="17" t="inlineStr">
+      <c r="P39" s="16" t="inlineStr"/>
+      <c r="Q39" s="16" t="inlineStr"/>
+      <c r="R39" s="16" t="inlineStr"/>
+      <c r="S39" s="16" t="inlineStr"/>
+      <c r="T39" s="16" t="inlineStr">
+        <is>
+          <t>aichaamghar198@gmail.com</t>
+        </is>
+      </c>
+      <c r="U39" s="16" t="inlineStr">
+        <is>
+          <t>Aicha</t>
+        </is>
+      </c>
+      <c r="V39" s="16" t="inlineStr">
+        <is>
+          <t>Amghar</t>
+        </is>
+      </c>
+      <c r="W39" s="16" t="inlineStr">
+        <is>
+          <t>+34602370988</t>
+        </is>
+      </c>
+      <c r="X39" s="16" t="inlineStr">
         <is>
           <t>First Order</t>
         </is>
       </c>
-      <c r="Y39" s="17" t="inlineStr">
+      <c r="Y39" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z39" s="17" t="inlineStr"/>
-      <c r="AA39" s="17" t="inlineStr"/>
-      <c r="AB39" s="17" t="inlineStr"/>
-      <c r="AC39" s="17" t="inlineStr"/>
-      <c r="AD39" s="17" t="inlineStr"/>
-      <c r="AE39" s="17" t="inlineStr"/>
-      <c r="AF39" s="17" t="inlineStr"/>
+      <c r="Z39" s="16" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="AA39" s="16" t="inlineStr"/>
+      <c r="AB39" s="16" t="inlineStr"/>
+      <c r="AC39" s="16" t="inlineStr"/>
+      <c r="AD39" s="16" t="inlineStr"/>
+      <c r="AE39" s="16" t="inlineStr"/>
+      <c r="AF39" s="16" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="n">
-        <v>320</v>
-      </c>
-      <c r="C40" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="D40" s="20" t="n">
-        <v>4.8</v>
+          <t>Pashion.dk ApS</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>1.49</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>09/04/25 19:12</t>
+          <t>09/05/25 16:59</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>77301</t>
+          <t>6877597237589</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -6026,24 +6030,24 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I40" s="21" t="inlineStr">
+      <c r="I40" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Air Jordan 3 Retro Black Cat</t>
+          <t>Adidas Handball Spezial Earth Strata Gum</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>41 EU - 8 US</t>
+          <t>38 EU - 5.5 US</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CT8532-001</t>
+          <t>IF6490</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -6067,22 +6071,22 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
-          <t>alexitomendo1960@gmail.com</t>
+          <t>tatiana7201@gmail.com</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Tatiana</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Silva Aragonés</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>+34634868685</t>
+          <t>+34618535989</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -6095,16 +6099,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>an unknown source</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>webgains</t>
-        </is>
-      </c>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
@@ -6112,144 +6108,144 @@
       <c r="AF40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>BlueVision Interactive Limited</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="n">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Purplee Corp</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n">
         <v>120</v>
       </c>
-      <c r="C41" s="18" t="n">
+      <c r="C41" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D41" s="18" t="n">
+      <c r="D41" s="17" t="n">
         <v>1.8</v>
       </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>09/05/25 20:13</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>77431</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>09/02/25 21:53</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>6870936355157</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H41" s="17" t="inlineStr">
+      <c r="H41" s="16" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I41" s="19" t="inlineStr">
+      <c r="I41" s="18" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="J41" s="17" t="inlineStr">
+      <c r="J41" s="16" t="inlineStr">
         <is>
           <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
         </is>
       </c>
-      <c r="K41" s="17" t="inlineStr">
-        <is>
-          <t>43 EU - 10 US</t>
-        </is>
-      </c>
-      <c r="L41" s="17" t="inlineStr">
+      <c r="K41" s="16" t="inlineStr">
+        <is>
+          <t>41 EU - 8.5 US</t>
+        </is>
+      </c>
+      <c r="L41" s="16" t="inlineStr">
         <is>
           <t>310864-01</t>
         </is>
       </c>
-      <c r="M41" s="17" t="inlineStr">
+      <c r="M41" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N41" s="17" t="inlineStr">
+      <c r="N41" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O41" s="17" t="inlineStr">
+      <c r="O41" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P41" s="17" t="inlineStr"/>
-      <c r="Q41" s="17" t="inlineStr"/>
-      <c r="R41" s="17" t="inlineStr"/>
-      <c r="S41" s="17" t="inlineStr"/>
-      <c r="T41" s="17" t="inlineStr">
-        <is>
-          <t>pj_sanchez17@yahoo.es</t>
-        </is>
-      </c>
-      <c r="U41" s="17" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="V41" s="17" t="inlineStr">
-        <is>
-          <t>Sanchez fernandez</t>
-        </is>
-      </c>
-      <c r="W41" s="17" t="inlineStr">
-        <is>
-          <t>+34655472907</t>
-        </is>
-      </c>
-      <c r="X41" s="17" t="inlineStr">
-        <is>
-          <t>Repeat Customer (Order #2)</t>
-        </is>
-      </c>
-      <c r="Y41" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z41" s="17" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="AA41" s="17" t="inlineStr"/>
-      <c r="AB41" s="17" t="inlineStr"/>
-      <c r="AC41" s="17" t="inlineStr"/>
-      <c r="AD41" s="17" t="inlineStr"/>
-      <c r="AE41" s="17" t="inlineStr"/>
-      <c r="AF41" s="17" t="inlineStr"/>
+      <c r="P41" s="16" t="inlineStr"/>
+      <c r="Q41" s="16" t="inlineStr"/>
+      <c r="R41" s="16" t="inlineStr"/>
+      <c r="S41" s="16" t="inlineStr"/>
+      <c r="T41" s="16" t="inlineStr">
+        <is>
+          <t>sandrafresita@live.com</t>
+        </is>
+      </c>
+      <c r="U41" s="16" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="V41" s="16" t="inlineStr">
+        <is>
+          <t>Sáez badia</t>
+        </is>
+      </c>
+      <c r="W41" s="16" t="inlineStr">
+        <is>
+          <t>+34660229457</t>
+        </is>
+      </c>
+      <c r="X41" s="16" t="inlineStr">
+        <is>
+          <t>First Order</t>
+        </is>
+      </c>
+      <c r="Y41" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z41" s="16" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="AA41" s="16" t="inlineStr"/>
+      <c r="AB41" s="16" t="inlineStr"/>
+      <c r="AC41" s="16" t="inlineStr"/>
+      <c r="AD41" s="16" t="inlineStr"/>
+      <c r="AE41" s="16" t="inlineStr"/>
+      <c r="AF41" s="16" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="n">
-        <v>120</v>
-      </c>
-      <c r="C42" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="D42" s="20" t="n">
-        <v>1.8</v>
+          <t>Invoke AB</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>320</v>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>4.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>09/02/25 21:53</t>
+          <t>09/04/25 19:12</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>6870936355157</t>
+          <t>77301</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6262,24 +6258,24 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I42" s="21" t="inlineStr">
+      <c r="I42" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Puma LaMelo Ball LaFrancé Amour Moment</t>
+          <t>Air Jordan 3 Retro Black Cat</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>41 EU - 8.5 US</t>
+          <t>41 EU - 8 US</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>310864-01</t>
+          <t>CT8532-001</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -6303,22 +6299,22 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
-          <t>sandrafresita@live.com</t>
+          <t>alexitomendo1960@gmail.com</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Sáez badia</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>+34660229457</t>
+          <t>+34634868685</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -6333,10 +6329,14 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr"/>
+          <t>an unknown source</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>webgains</t>
+        </is>
+      </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
@@ -6344,120 +6344,120 @@
       <c r="AF42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>BlueVision Interactive Limited</t>
         </is>
       </c>
-      <c r="B43" s="18" t="n">
+      <c r="B43" s="17" t="n">
         <v>250</v>
       </c>
-      <c r="C43" s="18" t="n">
+      <c r="C43" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="D43" s="18" t="n">
+      <c r="D43" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="E43" s="16" t="inlineStr">
         <is>
           <t>09/04/25 16:31</t>
         </is>
       </c>
-      <c r="F43" s="17" t="inlineStr">
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>77278</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr">
+      <c r="G43" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H43" s="17" t="inlineStr">
+      <c r="H43" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I43" s="19" t="inlineStr">
+      <c r="I43" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="J43" s="17" t="inlineStr">
+      <c r="J43" s="16" t="inlineStr">
         <is>
           <t>Air Jordan 3 Retro Pure Money</t>
         </is>
       </c>
-      <c r="K43" s="17" t="inlineStr">
+      <c r="K43" s="16" t="inlineStr">
         <is>
           <t>41 EU - 8 US</t>
         </is>
       </c>
-      <c r="L43" s="17" t="inlineStr">
+      <c r="L43" s="16" t="inlineStr">
         <is>
           <t>CT8532-111</t>
         </is>
       </c>
-      <c r="M43" s="17" t="inlineStr">
+      <c r="M43" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N43" s="17" t="inlineStr">
+      <c r="N43" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O43" s="17" t="inlineStr">
+      <c r="O43" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P43" s="17" t="inlineStr"/>
-      <c r="Q43" s="17" t="inlineStr"/>
-      <c r="R43" s="17" t="inlineStr"/>
-      <c r="S43" s="17" t="inlineStr"/>
-      <c r="T43" s="17" t="inlineStr">
+      <c r="P43" s="16" t="inlineStr"/>
+      <c r="Q43" s="16" t="inlineStr"/>
+      <c r="R43" s="16" t="inlineStr"/>
+      <c r="S43" s="16" t="inlineStr"/>
+      <c r="T43" s="16" t="inlineStr">
         <is>
           <t>sebastiancalvovinasco076@gmail.com</t>
         </is>
       </c>
-      <c r="U43" s="17" t="inlineStr">
+      <c r="U43" s="16" t="inlineStr">
         <is>
           <t>Sebastian</t>
         </is>
       </c>
-      <c r="V43" s="17" t="inlineStr">
+      <c r="V43" s="16" t="inlineStr">
         <is>
           <t>Calvo vinasco</t>
         </is>
       </c>
-      <c r="W43" s="17" t="inlineStr">
+      <c r="W43" s="16" t="inlineStr">
         <is>
           <t>+34655364031</t>
         </is>
       </c>
-      <c r="X43" s="17" t="inlineStr">
+      <c r="X43" s="16" t="inlineStr">
         <is>
           <t>Repeat Customer (Order #3)</t>
         </is>
       </c>
-      <c r="Y43" s="17" t="inlineStr">
+      <c r="Y43" s="16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Z43" s="17" t="inlineStr">
+      <c r="Z43" s="16" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="AA43" s="17" t="inlineStr"/>
-      <c r="AB43" s="17" t="inlineStr"/>
-      <c r="AC43" s="17" t="inlineStr"/>
-      <c r="AD43" s="17" t="inlineStr"/>
-      <c r="AE43" s="17" t="inlineStr"/>
-      <c r="AF43" s="17" t="inlineStr"/>
+      <c r="AA43" s="16" t="inlineStr"/>
+      <c r="AB43" s="16" t="inlineStr"/>
+      <c r="AC43" s="16" t="inlineStr"/>
+      <c r="AD43" s="16" t="inlineStr"/>
+      <c r="AE43" s="16" t="inlineStr"/>
+      <c r="AF43" s="16" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6465,13 +6465,13 @@
           <t>Skimbit LTD</t>
         </is>
       </c>
-      <c r="B44" s="20" t="n">
+      <c r="B44" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="C44" s="20" t="n">
+      <c r="C44" s="14" t="n">
         <v>4.8</v>
       </c>
-      <c r="D44" s="20" t="n">
+      <c r="D44" s="14" t="n">
         <v>1.44</v>
       </c>
       <c r="E44" t="inlineStr">
@@ -6494,7 +6494,7 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I44" s="21" t="inlineStr">
+      <c r="I44" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>an unknown source</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6580,120 +6580,120 @@
       <c r="AF44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>AFILIZA</t>
         </is>
       </c>
-      <c r="B45" s="18" t="n">
+      <c r="B45" s="17" t="n">
         <v>360</v>
       </c>
-      <c r="C45" s="18" t="n">
+      <c r="C45" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="D45" s="18" t="n">
+      <c r="D45" s="17" t="n">
         <v>5.4</v>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="E45" s="16" t="inlineStr">
         <is>
           <t>09/01/25 23:16</t>
         </is>
       </c>
-      <c r="F45" s="17" t="inlineStr">
+      <c r="F45" s="16" t="inlineStr">
         <is>
           <t>77062</t>
         </is>
       </c>
-      <c r="G45" s="17" t="inlineStr">
+      <c r="G45" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H45" s="17" t="inlineStr">
+      <c r="H45" s="16" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I45" s="19" t="inlineStr">
+      <c r="I45" s="18" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="J45" s="17" t="inlineStr">
+      <c r="J45" s="16" t="inlineStr">
         <is>
           <t>Pop Mart Labubu The Monsters Big into Energy Series, Pop Mart Labubu The Monsters Coca Cola Series</t>
         </is>
       </c>
-      <c r="K45" s="17" t="inlineStr">
+      <c r="K45" s="16" t="inlineStr">
         <is>
           <t>Whole Set, Single Box</t>
         </is>
       </c>
-      <c r="L45" s="17" t="inlineStr">
+      <c r="L45" s="16" t="inlineStr">
         <is>
           <t>PPMTBES, PPMTCC</t>
         </is>
       </c>
-      <c r="M45" s="17" t="inlineStr">
+      <c r="M45" s="16" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="N45" s="17" t="inlineStr">
+      <c r="N45" s="16" t="inlineStr">
         <is>
           <t>FULFILLED</t>
         </is>
       </c>
-      <c r="O45" s="17" t="inlineStr">
+      <c r="O45" s="16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P45" s="17" t="inlineStr"/>
-      <c r="Q45" s="17" t="inlineStr"/>
-      <c r="R45" s="17" t="inlineStr"/>
-      <c r="S45" s="17" t="inlineStr"/>
-      <c r="T45" s="17" t="inlineStr">
+      <c r="P45" s="16" t="inlineStr"/>
+      <c r="Q45" s="16" t="inlineStr"/>
+      <c r="R45" s="16" t="inlineStr"/>
+      <c r="S45" s="16" t="inlineStr"/>
+      <c r="T45" s="16" t="inlineStr">
         <is>
           <t>iresteve@gmail.com</t>
         </is>
       </c>
-      <c r="U45" s="17" t="inlineStr">
+      <c r="U45" s="16" t="inlineStr">
         <is>
           <t>Irene</t>
         </is>
       </c>
-      <c r="V45" s="17" t="inlineStr">
+      <c r="V45" s="16" t="inlineStr">
         <is>
           <t>Esteve Munoz</t>
         </is>
       </c>
-      <c r="W45" s="17" t="inlineStr">
+      <c r="W45" s="16" t="inlineStr">
         <is>
           <t>+34655032069</t>
         </is>
       </c>
-      <c r="X45" s="17" t="inlineStr">
+      <c r="X45" s="16" t="inlineStr">
         <is>
           <t>Repeat Customer (Order #2)</t>
         </is>
       </c>
-      <c r="Y45" s="17" t="inlineStr">
+      <c r="Y45" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z45" s="17" t="inlineStr">
+      <c r="Z45" s="16" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="AA45" s="17" t="inlineStr"/>
-      <c r="AB45" s="17" t="inlineStr"/>
-      <c r="AC45" s="17" t="inlineStr"/>
-      <c r="AD45" s="17" t="inlineStr"/>
-      <c r="AE45" s="17" t="inlineStr"/>
-      <c r="AF45" s="17" t="inlineStr"/>
+      <c r="AA45" s="16" t="inlineStr"/>
+      <c r="AB45" s="16" t="inlineStr"/>
+      <c r="AC45" s="16" t="inlineStr"/>
+      <c r="AD45" s="16" t="inlineStr"/>
+      <c r="AE45" s="16" t="inlineStr"/>
+      <c r="AF45" s="16" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6701,13 +6701,13 @@
           <t>LINKGAINS PTE.LTD.</t>
         </is>
       </c>
-      <c r="B46" s="20" t="n">
+      <c r="B46" s="14" t="n">
         <v>99</v>
       </c>
-      <c r="C46" s="20" t="n">
+      <c r="C46" s="14" t="n">
         <v>4.95</v>
       </c>
-      <c r="D46" s="20" t="n">
+      <c r="D46" s="14" t="n">
         <v>1.49</v>
       </c>
       <c r="E46" t="inlineStr">
@@ -6730,7 +6730,7 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I46" s="21" t="inlineStr">
+      <c r="I46" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -6902,26 +6902,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Skimbit LTD</t>
-        </is>
-      </c>
-      <c r="B2" s="20" t="n">
-        <v>429</v>
-      </c>
-      <c r="C2" s="20" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="D2" s="20" t="n">
-        <v>6.73</v>
+          <t>Digital Expand</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="C2" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D2" s="14" t="n">
+        <v>1.26</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09/30/25 21:03</t>
+          <t>09/30/25 12:49</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>79415</t>
+          <t>79361</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6931,51 +6931,51 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I2" s="21" t="inlineStr">
-        <is>
-          <t>5%</t>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I2" s="15" t="inlineStr">
+        <is>
+          <t>6%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Digital Expand</t>
         </is>
       </c>
-      <c r="B3" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="C3" s="18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D3" s="18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>09/30/25 12:49</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>79361</t>
-        </is>
-      </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="B3" s="17" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>09/30/25 16:25</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>79375</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -6984,82 +6984,82 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Skimbit LTD</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>429</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>09/30/25 21:03</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>79415</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
           <t>BlueVision Interactive Limited</t>
         </is>
       </c>
-      <c r="B4" s="20" t="n">
+      <c r="B5" s="17" t="n">
         <v>380</v>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C5" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D5" s="17" t="n">
         <v>5.7</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>09/26/25 15:13</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>79025</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I4" s="21" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Digital Expand</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n">
-        <v>127.5</v>
-      </c>
-      <c r="C5" s="18" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="D5" s="18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>09/30/25 16:25</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>79375</t>
-        </is>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I5" s="19" t="inlineStr">
-        <is>
-          <t>6%</t>
         </is>
       </c>
     </row>
@@ -7069,13 +7069,13 @@
           <t>Mathias Kraft</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="14" t="n">
         <v>180</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="14" t="n">
         <v>10.8</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="14" t="n">
         <v>3.24</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -7098,50 +7098,50 @@
           <t>Retail</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>BlueVision Interactive Limited</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="n">
-        <v>330</v>
-      </c>
-      <c r="C7" s="18" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="D7" s="18" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>09/24/25 14:24</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>78891</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Webravo SRL</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>09/24/25 19:56</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>78931</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>6%</t>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>5%</t>
         </is>
       </c>
     </row>
@@ -7151,23 +7151,23 @@
           <t>Webravo SRL</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
-        <v>96</v>
-      </c>
-      <c r="C8" s="20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="D8" s="20" t="n">
-        <v>1.44</v>
+      <c r="B8" s="14" t="n">
+        <v>170</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>2.55</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>09/24/25 19:56</t>
+          <t>09/24/25 10:57</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>78931</t>
+          <t>78876</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7180,48 +7180,48 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>Webravo SRL</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="n">
-        <v>99</v>
-      </c>
-      <c r="C9" s="18" t="n">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>BlueVision Interactive Limited</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>330</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D9" s="17" t="n">
         <v>5.94</v>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>09/23/25 11:28</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>78821</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>09/24/25 14:24</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>78891</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -7233,23 +7233,23 @@
           <t>Webravo SRL</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
-        <v>170</v>
-      </c>
-      <c r="C10" s="20" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>2.55</v>
+      <c r="B10" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>1.78</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>09/24/25 10:57</t>
+          <t>09/23/25 11:28</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>78876</t>
+          <t>78821</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -7259,51 +7259,51 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I10" s="21" t="inlineStr">
-        <is>
-          <t>5%</t>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>6%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Webravo SRL</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="17" t="n">
         <v>110</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="17" t="n">
         <v>6.6</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="17" t="n">
         <v>1.98</v>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>09/22/25 20:03</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>78812</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -7315,13 +7315,13 @@
           <t>Purplee Corp</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="14" t="n">
         <v>170</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="14" t="n">
         <v>10.2</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="14" t="n">
         <v>3.06</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -7344,48 +7344,48 @@
           <t>Retail</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Invoke AB</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="17" t="n">
         <v>350</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="17" t="n">
         <v>6.3</v>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>09/20/25 11:34</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>6900010221909</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -7397,13 +7397,13 @@
           <t>Digital Expand</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="14" t="n">
         <v>120</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="14" t="n">
         <v>1.8</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -7426,48 +7426,48 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Webravo SRL</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="17" t="n">
         <v>90</v>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="17" t="n">
         <v>5.4</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="17" t="n">
         <v>1.62</v>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>09/20/25 11:53</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>78608</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I15" s="19" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -7476,80 +7476,80 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>BlueVision Interactive Limited</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>09/19/25 23:39</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>78602</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
           <t>Pashion.dk ApS</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B17" s="17" t="n">
         <v>280</v>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C17" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D17" s="17" t="n">
         <v>4.2</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>09/16/25 20:51</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>6894848966997</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>LINKGAINS PTE.LTD.</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="n">
-        <v>120</v>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>09/17/25 21:49</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>78504</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I17" s="19" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -7558,80 +7558,80 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BlueVision Interactive Limited</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="n">
-        <v>110</v>
-      </c>
-      <c r="C18" s="20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="D18" s="20" t="n">
-        <v>1.98</v>
+          <t>LINKGAINS PTE.LTD.</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>1.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>09/19/25 23:39</t>
+          <t>09/17/25 21:49</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>78602</t>
+          <t>78504</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Pashion.dk ApS</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>09/16/25 16:05</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>78437</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Pashion.dk ApS</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="n">
-        <v>120</v>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>09/16/25 16:05</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>78437</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I19" s="19" t="inlineStr">
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -7640,26 +7640,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LINKGAINS PTE.LTD.</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="n">
-        <v>165</v>
-      </c>
-      <c r="C20" s="20" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="D20" s="20" t="n">
-        <v>2.97</v>
+          <t>BlueVision Interactive Limited</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>88</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>1.58</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>09/16/25 15:09</t>
+          <t>09/15/25 11:50</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>78430</t>
+          <t>78383</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7672,76 +7672,76 @@
           <t>Retail</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>BlueVision Interactive Limited</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="C21" s="18" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>09/15/25 11:50</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>78383</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Pashion.dk ApS</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>09/15/25 11:46</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>78382</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>6%</t>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="C22" s="20" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="D22" s="20" t="n">
-        <v>1.49</v>
+          <t>BlueVision Interactive Limited</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>96</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>1.73</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>09/14/25 12:50</t>
+          <t>09/14/25 22:07</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6891134681429</t>
+          <t>78374</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7754,48 +7754,48 @@
           <t>Retail</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I22" s="15" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>BlueVision Interactive Limited</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>09/14/25 22:07</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>78374</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>LINKGAINS PTE.LTD.</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>165</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>09/16/25 15:09</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>78430</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I23" s="19" t="inlineStr">
+      <c r="I23" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -7804,26 +7804,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pashion.dk ApS</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="n">
-        <v>120</v>
-      </c>
-      <c r="C24" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="D24" s="20" t="n">
-        <v>1.8</v>
+          <t>Purplee Corp</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>1.49</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>09/15/25 11:46</t>
+          <t>09/14/25 12:50</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>78382</t>
+          <t>6891134681429</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7833,51 +7833,51 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Digital Expand</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>550</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>09/11/25 16:14</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>6887025475925</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>BlueVision Interactive Limited</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="n">
-        <v>750</v>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>09/13/25 10:43</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>78157</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I25" s="19" t="inlineStr">
+      <c r="I25" s="18" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -7886,26 +7886,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Digital Expand</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="n">
-        <v>550</v>
-      </c>
-      <c r="C26" s="20" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="D26" s="20" t="n">
-        <v>8.25</v>
+          <t>BlueVision Interactive Limited</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>750</v>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>11.25</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>09/11/25 16:14</t>
+          <t>09/13/25 10:43</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6887025475925</t>
+          <t>78157</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7918,48 +7918,48 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="I26" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Shoparize</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="17" t="n">
         <v>85</v>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C27" s="17" t="n">
         <v>5.1</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="17" t="n">
         <v>1.53</v>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>09/10/25 16:40</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>77926</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G27" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I27" s="19" t="inlineStr">
+      <c r="I27" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -7968,162 +7968,162 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Klarna Bank AB UK Branch</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>153</v>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>09/10/25 09:03</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>77873</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
           <t>SID Middle East LLC</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
+      <c r="B29" s="17" t="n">
         <v>120.42</v>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C29" s="17" t="n">
         <v>7.23</v>
       </c>
-      <c r="D28" s="20" t="n">
+      <c r="D29" s="17" t="n">
         <v>2.17</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>09/10/25 11:03</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>77880</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" s="16" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I29" s="18" t="inlineStr">
         <is>
           <t>6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Klarna Bank AB UK Branch</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="n">
-        <v>153</v>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>09/10/25 09:03</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>77873</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I29" s="19" t="inlineStr">
-        <is>
-          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Skimbit LTD</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>09/09/25 21:51</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>77865</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
           <t>LINKGAINS PTE.LTD.</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
+      <c r="B31" s="17" t="n">
         <v>335</v>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C31" s="17" t="n">
         <v>16.75</v>
       </c>
-      <c r="D30" s="20" t="n">
+      <c r="D31" s="17" t="n">
         <v>5.03</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>09/09/25 17:32</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>77821</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" s="16" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I30" s="21" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Skimbit LTD</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>09/09/25 21:51</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>77865</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
+      <c r="I31" s="18" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -8135,13 +8135,13 @@
           <t>Webravo SRL</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n">
+      <c r="B32" s="14" t="n">
         <v>85</v>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C32" s="14" t="n">
         <v>5.1</v>
       </c>
-      <c r="D32" s="20" t="n">
+      <c r="D32" s="14" t="n">
         <v>1.53</v>
       </c>
       <c r="E32" t="inlineStr">
@@ -8164,48 +8164,48 @@
           <t>Retail</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
+      <c r="I32" s="15" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Skimbit LTD</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="17" t="n">
         <v>88</v>
       </c>
-      <c r="C33" s="18" t="n">
+      <c r="C33" s="17" t="n">
         <v>5.28</v>
       </c>
-      <c r="D33" s="18" t="n">
+      <c r="D33" s="17" t="n">
         <v>1.58</v>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>09/08/25 11:06</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>77687</t>
         </is>
       </c>
-      <c r="G33" s="17" t="inlineStr">
+      <c r="G33" s="16" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="H33" s="17" t="inlineStr">
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I33" s="19" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -8214,26 +8214,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LINKPREFER LIMITED</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="n">
-        <v>280</v>
-      </c>
-      <c r="C34" s="20" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="D34" s="20" t="n">
-        <v>5.04</v>
+          <t>Shoparize</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>1.26</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>09/07/25 15:13</t>
+          <t>09/09/25 01:55</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>77607</t>
+          <t>77760</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8246,48 +8246,48 @@
           <t>Retail</t>
         </is>
       </c>
-      <c r="I34" s="21" t="inlineStr">
+      <c r="I34" s="15" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>LINKGAINS PTE.LTD.</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>09/07/25 15:51</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>77615</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Fullstaak SA</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="C35" s="17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>09/06/25 16:11</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>6879153488213</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H35" s="17" t="inlineStr">
+      <c r="H35" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I35" s="19" t="inlineStr">
+      <c r="I35" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -8296,26 +8296,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="C36" s="20" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="D36" s="20" t="n">
-        <v>1.24</v>
+          <t>LINKPREFER LIMITED</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>280</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>5.04</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>09/07/25 14:43</t>
+          <t>09/07/25 15:13</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>77604</t>
+          <t>77607</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -8325,51 +8325,51 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Reventa</t>
-        </is>
-      </c>
-      <c r="I36" s="21" t="inlineStr">
-        <is>
-          <t>5%</t>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>6%</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>Shoparize</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="C37" s="18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>09/09/25 01:55</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>77760</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>LINKGAINS PTE.LTD.</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>09/07/25 15:51</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>77615</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
+      <c r="H37" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I37" s="19" t="inlineStr">
+      <c r="I37" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -8378,26 +8378,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fullstaak SA</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="C38" s="20" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="D38" s="20" t="n">
-        <v>1.22</v>
+          <t>BlueVision Interactive Limited</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>1.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>09/06/25 16:11</t>
+          <t>09/05/25 20:13</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>6879153488213</t>
+          <t>77431</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -8407,51 +8407,51 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="I38" s="21" t="inlineStr">
-        <is>
-          <t>6%</t>
+          <t>Reventa</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>Pashion.dk ApS</t>
-        </is>
-      </c>
-      <c r="B39" s="18" t="n">
-        <v>99</v>
-      </c>
-      <c r="C39" s="18" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>09/05/25 16:59</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>6877597237589</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Purplee Corp</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>09/07/25 14:43</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>77604</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H39" s="17" t="inlineStr">
+      <c r="H39" s="16" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I39" s="19" t="inlineStr">
+      <c r="I39" s="18" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -8460,26 +8460,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Invoke AB</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="n">
-        <v>320</v>
-      </c>
-      <c r="C40" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="D40" s="20" t="n">
-        <v>4.8</v>
+          <t>Pashion.dk ApS</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>1.49</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>09/04/25 19:12</t>
+          <t>09/05/25 16:59</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>77301</t>
+          <t>6877597237589</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -8492,48 +8492,48 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I40" s="21" t="inlineStr">
+      <c r="I40" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>BlueVision Interactive Limited</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="n">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Purplee Corp</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n">
         <v>120</v>
       </c>
-      <c r="C41" s="18" t="n">
+      <c r="C41" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D41" s="18" t="n">
+      <c r="D41" s="17" t="n">
         <v>1.8</v>
       </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>09/05/25 20:13</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>77431</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>09/02/25 21:53</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>6870936355157</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H41" s="17" t="inlineStr">
+      <c r="H41" s="16" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I41" s="19" t="inlineStr">
+      <c r="I41" s="18" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -8542,26 +8542,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Purplee Corp</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="n">
-        <v>120</v>
-      </c>
-      <c r="C42" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="D42" s="20" t="n">
-        <v>1.8</v>
+          <t>Invoke AB</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>320</v>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>4.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>09/02/25 21:53</t>
+          <t>09/04/25 19:12</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>6870936355157</t>
+          <t>77301</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -8574,48 +8574,48 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I42" s="21" t="inlineStr">
+      <c r="I42" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>BlueVision Interactive Limited</t>
         </is>
       </c>
-      <c r="B43" s="18" t="n">
+      <c r="B43" s="17" t="n">
         <v>250</v>
       </c>
-      <c r="C43" s="18" t="n">
+      <c r="C43" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="D43" s="18" t="n">
+      <c r="D43" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="E43" s="16" t="inlineStr">
         <is>
           <t>09/04/25 16:31</t>
         </is>
       </c>
-      <c r="F43" s="17" t="inlineStr">
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>77278</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr">
+      <c r="G43" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H43" s="17" t="inlineStr">
+      <c r="H43" s="16" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="I43" s="19" t="inlineStr">
+      <c r="I43" s="18" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -8627,13 +8627,13 @@
           <t>Skimbit LTD</t>
         </is>
       </c>
-      <c r="B44" s="20" t="n">
+      <c r="B44" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="C44" s="20" t="n">
+      <c r="C44" s="14" t="n">
         <v>4.8</v>
       </c>
-      <c r="D44" s="20" t="n">
+      <c r="D44" s="14" t="n">
         <v>1.44</v>
       </c>
       <c r="E44" t="inlineStr">
@@ -8656,48 +8656,48 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I44" s="21" t="inlineStr">
+      <c r="I44" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>AFILIZA</t>
         </is>
       </c>
-      <c r="B45" s="18" t="n">
+      <c r="B45" s="17" t="n">
         <v>360</v>
       </c>
-      <c r="C45" s="18" t="n">
+      <c r="C45" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="D45" s="18" t="n">
+      <c r="D45" s="17" t="n">
         <v>5.4</v>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="E45" s="16" t="inlineStr">
         <is>
           <t>09/01/25 23:16</t>
         </is>
       </c>
-      <c r="F45" s="17" t="inlineStr">
+      <c r="F45" s="16" t="inlineStr">
         <is>
           <t>77062</t>
         </is>
       </c>
-      <c r="G45" s="17" t="inlineStr">
+      <c r="G45" s="16" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H45" s="17" t="inlineStr">
+      <c r="H45" s="16" t="inlineStr">
         <is>
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I45" s="19" t="inlineStr">
+      <c r="I45" s="18" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -8709,13 +8709,13 @@
           <t>LINKGAINS PTE.LTD.</t>
         </is>
       </c>
-      <c r="B46" s="20" t="n">
+      <c r="B46" s="14" t="n">
         <v>99</v>
       </c>
-      <c r="C46" s="20" t="n">
+      <c r="C46" s="14" t="n">
         <v>4.95</v>
       </c>
-      <c r="D46" s="20" t="n">
+      <c r="D46" s="14" t="n">
         <v>1.49</v>
       </c>
       <c r="E46" t="inlineStr">
@@ -8738,7 +8738,7 @@
           <t>Reventa</t>
         </is>
       </c>
-      <c r="I46" s="21" t="inlineStr">
+      <c r="I46" s="15" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
